--- a/db/A7XLK-1111-HouseApp3.xlsx
+++ b/db/A7XLK-1111-HouseApp3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0F1257-C007-0F4D-98F4-18A025C3B725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CC8D1E-9C0B-1F4F-A29A-7191CE23D7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4560" yWindow="-17480" windowWidth="27320" windowHeight="16380" xr2:uid="{33D194D6-A429-7949-A97B-0894189945E2}"/>
+    <workbookView xWindow="980" yWindow="-18340" windowWidth="27320" windowHeight="16380" xr2:uid="{33D194D6-A429-7949-A97B-0894189945E2}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="754">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1906,10 +1906,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://newhouse.591.com.tw/home/housing/info?hid=122055</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>30萬元/坪</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2976,6 +2972,18 @@
   </si>
   <si>
     <t>銷售量</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://newhouse.591.com.tw/home/housing/detail?hid=122055</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完售</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3512,7 +3520,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>8</v>
@@ -3724,7 +3732,9 @@
       <c r="H2" s="13">
         <v>23.38</v>
       </c>
-      <c r="I2" s="13"/>
+      <c r="I2" s="13">
+        <v>207</v>
+      </c>
       <c r="J2" s="14">
         <v>26.49</v>
       </c>
@@ -3928,7 +3938,7 @@
         <v>142</v>
       </c>
       <c r="I3" s="22">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="J3" s="21">
         <v>26.27</v>
@@ -4135,7 +4145,9 @@
       <c r="H4" s="13">
         <v>25.01</v>
       </c>
-      <c r="I4" s="13"/>
+      <c r="I4" s="13">
+        <v>206</v>
+      </c>
       <c r="J4" s="14">
         <v>27.55</v>
       </c>
@@ -4330,13 +4342,15 @@
         <v>489</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>490</v>
+        <v>751</v>
       </c>
       <c r="G5" s="21"/>
       <c r="H5" s="22">
         <v>24.99</v>
       </c>
-      <c r="I5" s="22"/>
+      <c r="I5" s="22">
+        <v>157</v>
+      </c>
       <c r="J5" s="21">
         <v>27.76</v>
       </c>
@@ -4344,7 +4358,7 @@
         <v>22.52</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="M5" s="15">
         <v>30</v>
@@ -4361,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="R5" s="15">
         <v>30</v>
@@ -4378,7 +4392,7 @@
         <v>30</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AA5" s="16">
         <v>160</v>
@@ -4393,7 +4407,7 @@
         <v>77</v>
       </c>
       <c r="AE5" s="9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AF5" s="10">
         <v>2022</v>
@@ -4405,7 +4419,7 @@
         <v>80</v>
       </c>
       <c r="AI5" s="9" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AJ5" s="9" t="s">
         <v>171</v>
@@ -4417,28 +4431,28 @@
         <v>117</v>
       </c>
       <c r="AM5" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="AN5" s="26" t="s">
+        <v>494</v>
+      </c>
+      <c r="AO5" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="AN5" s="26" t="s">
-        <v>495</v>
-      </c>
-      <c r="AO5" s="9" t="s">
+      <c r="AP5" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="AP5" s="9" t="s">
+      <c r="AQ5" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="AR5" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="AQ5" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="AR5" s="9" t="s">
+      <c r="AS5" s="9" t="s">
         <v>498</v>
       </c>
-      <c r="AS5" s="9" t="s">
+      <c r="AT5" s="9" t="s">
         <v>499</v>
-      </c>
-      <c r="AT5" s="9" t="s">
-        <v>500</v>
       </c>
       <c r="AU5" s="17">
         <v>0.32</v>
@@ -4447,7 +4461,7 @@
         <v>0.32</v>
       </c>
       <c r="AW5" s="9" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AX5" s="9">
         <v>154</v>
@@ -4468,13 +4482,13 @@
         <v>15</v>
       </c>
       <c r="BD5" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="BE5" s="9" t="s">
         <v>96</v>
       </c>
       <c r="BF5" s="11" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="BG5" s="19">
         <v>1.17</v>
@@ -4483,7 +4497,7 @@
         <v>98</v>
       </c>
       <c r="BI5" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="BJ5" s="9">
         <v>933.78</v>
@@ -4492,7 +4506,7 @@
         <v>100</v>
       </c>
       <c r="BL5" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="BM5" s="9" t="s">
         <v>102</v>
@@ -4501,10 +4515,10 @@
         <v>102</v>
       </c>
       <c r="BO5" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="BP5" s="9" t="s">
         <v>506</v>
-      </c>
-      <c r="BP5" s="9" t="s">
-        <v>507</v>
       </c>
       <c r="BQ5" s="9" t="s">
         <v>102</v>
@@ -4521,26 +4535,26 @@
         <v>409</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>411 和洲金剛</v>
       </c>
       <c r="E6" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>541</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>542</v>
       </c>
       <c r="G6" s="14">
         <v>26.33</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I6" s="13">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="J6" s="14">
         <v>28.67</v>
@@ -4549,7 +4563,7 @@
         <v>21.01</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="M6" s="15">
         <v>25</v>
@@ -4604,7 +4618,7 @@
         <v>80</v>
       </c>
       <c r="AI6" s="9" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AJ6" s="9" t="s">
         <v>116</v>
@@ -4616,16 +4630,16 @@
         <v>117</v>
       </c>
       <c r="AM6" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="AN6" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="AN6" s="9" t="s">
+      <c r="AO6" s="9" t="s">
         <v>547</v>
       </c>
-      <c r="AO6" s="9" t="s">
+      <c r="AP6" s="9" t="s">
         <v>548</v>
-      </c>
-      <c r="AP6" s="9" t="s">
-        <v>549</v>
       </c>
       <c r="AQ6" s="9" t="s">
         <v>89</v>
@@ -4634,7 +4648,7 @@
         <v>121</v>
       </c>
       <c r="AS6" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AT6" s="9" t="s">
         <v>137</v>
@@ -4646,7 +4660,7 @@
         <v>0.32</v>
       </c>
       <c r="AW6" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AX6" s="9">
         <v>210</v>
@@ -4655,19 +4669,19 @@
         <v>11</v>
       </c>
       <c r="AZ6" s="9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="BA6" s="18">
         <v>0.45540000000000003</v>
       </c>
       <c r="BB6" s="9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="BC6" s="9">
         <v>15</v>
       </c>
       <c r="BD6" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="BE6" s="9" t="s">
         <v>96</v>
@@ -4691,16 +4705,16 @@
         <v>100</v>
       </c>
       <c r="BL6" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="BM6" s="9" t="s">
         <v>555</v>
-      </c>
-      <c r="BM6" s="9" t="s">
-        <v>556</v>
       </c>
       <c r="BN6" s="9" t="s">
         <v>102</v>
       </c>
       <c r="BO6" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="BP6" s="9" t="s">
         <v>133</v>
@@ -4739,7 +4753,7 @@
         <v>278</v>
       </c>
       <c r="I7" s="13">
-        <v>134</v>
+        <v>243</v>
       </c>
       <c r="J7" s="14">
         <v>30.14</v>
@@ -4916,23 +4930,25 @@
         <v>409</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D8" s="12" t="str">
         <f t="shared" si="0"/>
         <v>409 新未來2</v>
       </c>
       <c r="E8" s="12" t="s">
+        <v>508</v>
+      </c>
+      <c r="F8" s="20" t="s">
         <v>509</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>510</v>
       </c>
       <c r="G8" s="21"/>
       <c r="H8" s="22">
         <v>26.39</v>
       </c>
-      <c r="I8" s="22"/>
+      <c r="I8" s="22">
+        <v>387</v>
+      </c>
       <c r="J8" s="21">
         <v>29.56</v>
       </c>
@@ -4940,7 +4956,7 @@
         <v>23.12</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="M8" s="15">
         <v>30</v>
@@ -4957,7 +4973,7 @@
         <v>1</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R8" s="15">
         <v>30</v>
@@ -4974,7 +4990,7 @@
         <v>31</v>
       </c>
       <c r="Z8" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AA8" s="16">
         <v>180</v>
@@ -4989,7 +5005,7 @@
         <v>77</v>
       </c>
       <c r="AE8" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AF8" s="10">
         <v>2022</v>
@@ -5001,7 +5017,7 @@
         <v>80</v>
       </c>
       <c r="AI8" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AJ8" s="9" t="s">
         <v>171</v>
@@ -5013,25 +5029,25 @@
         <v>117</v>
       </c>
       <c r="AM8" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="AN8" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="AN8" s="9" t="s">
+      <c r="AO8" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="AO8" s="9" t="s">
+      <c r="AP8" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="AP8" s="9" t="s">
+      <c r="AQ8" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AR8" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="AQ8" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="AR8" s="9" t="s">
+      <c r="AS8" s="9" t="s">
         <v>519</v>
-      </c>
-      <c r="AS8" s="9" t="s">
-        <v>520</v>
       </c>
       <c r="AT8" s="9" t="s">
         <v>465</v>
@@ -5043,7 +5059,7 @@
         <v>0.33</v>
       </c>
       <c r="AW8" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AX8" s="9">
         <v>376</v>
@@ -5064,7 +5080,7 @@
         <v>22</v>
       </c>
       <c r="BD8" s="18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="BE8" s="9" t="s">
         <v>182</v>
@@ -5079,7 +5095,7 @@
         <v>98</v>
       </c>
       <c r="BI8" s="9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="BJ8" s="9">
         <v>1955.56</v>
@@ -5097,10 +5113,10 @@
         <v>102</v>
       </c>
       <c r="BO8" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="BP8" s="9" t="s">
         <v>524</v>
-      </c>
-      <c r="BP8" s="9" t="s">
-        <v>525</v>
       </c>
       <c r="BQ8" s="9" t="s">
         <v>102</v>
@@ -5117,26 +5133,26 @@
         <v>409</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>412 君邑丘比特</v>
       </c>
       <c r="E9" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>559</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>560</v>
       </c>
       <c r="G9" s="14">
         <v>27.47</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I9" s="13">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="J9" s="14">
         <v>32.229999999999997</v>
@@ -5145,7 +5161,7 @@
         <v>22.94</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="M9" s="15">
         <v>27.8</v>
@@ -5162,7 +5178,7 @@
         <v>2.1000000000000014</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="R9" s="15">
         <v>29.8</v>
@@ -5179,7 +5195,7 @@
         <v>34</v>
       </c>
       <c r="Z9" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AA9" s="16">
         <v>180</v>
@@ -5194,7 +5210,7 @@
         <v>77</v>
       </c>
       <c r="AE9" s="9" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AF9" s="10">
         <v>2022</v>
@@ -5206,7 +5222,7 @@
         <v>80</v>
       </c>
       <c r="AI9" s="9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="AJ9" s="9" t="s">
         <v>171</v>
@@ -5215,40 +5231,40 @@
         <v>83</v>
       </c>
       <c r="AL9" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="AM9" s="9" t="s">
         <v>567</v>
       </c>
-      <c r="AM9" s="9" t="s">
+      <c r="AN9" s="9" t="s">
         <v>568</v>
       </c>
-      <c r="AN9" s="9" t="s">
+      <c r="AO9" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="AO9" s="9" t="s">
+      <c r="AP9" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="AP9" s="9" t="s">
+      <c r="AQ9" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="AR9" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="AQ9" s="9" t="s">
+      <c r="AS9" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="AR9" s="9" t="s">
+      <c r="AT9" s="9" t="s">
         <v>572</v>
       </c>
-      <c r="AS9" s="9" t="s">
-        <v>572</v>
-      </c>
-      <c r="AT9" s="9" t="s">
+      <c r="AU9" s="9" t="s">
         <v>573</v>
-      </c>
-      <c r="AU9" s="9" t="s">
-        <v>574</v>
       </c>
       <c r="AV9" s="18">
         <v>0.33129999999999998</v>
       </c>
       <c r="AW9" s="9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AX9" s="9">
         <v>173</v>
@@ -5263,19 +5279,19 @@
         <v>0.46150000000000002</v>
       </c>
       <c r="BB9" s="9" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="BC9" s="9">
         <v>15</v>
       </c>
       <c r="BD9" s="9" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="BE9" s="9" t="s">
         <v>96</v>
       </c>
       <c r="BF9" s="11" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="BG9" s="19">
         <v>1.07</v>
@@ -5284,7 +5300,7 @@
         <v>98</v>
       </c>
       <c r="BI9" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="BJ9" s="9">
         <v>1030.74</v>
@@ -5293,7 +5309,7 @@
         <v>100</v>
       </c>
       <c r="BL9" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BM9" s="9" t="s">
         <v>102</v>
@@ -5302,10 +5318,10 @@
         <v>102</v>
       </c>
       <c r="BO9" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="BP9" s="9" t="s">
         <v>580</v>
-      </c>
-      <c r="BP9" s="9" t="s">
-        <v>581</v>
       </c>
       <c r="BQ9" s="9" t="s">
         <v>102</v>
@@ -5322,17 +5338,20 @@
         <v>409</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D10" s="12" t="str">
         <f t="shared" ref="D10:D32" si="5">CONCATENATE(A10," ",C10)</f>
         <v>414 合謙學</v>
       </c>
       <c r="E10" s="12" t="s">
+        <v>600</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>601</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>602</v>
+      <c r="I10" s="13">
+        <v>96</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>456</v>
@@ -5352,7 +5371,7 @@
         <v>1.5</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R10" s="15">
         <v>35</v>
@@ -5390,7 +5409,7 @@
         <v>80</v>
       </c>
       <c r="AI10" s="9" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AJ10" s="9" t="s">
         <v>171</v>
@@ -5399,31 +5418,31 @@
         <v>83</v>
       </c>
       <c r="AL10" s="9" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AM10" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="AN10" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="AO10" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="AN10" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="AO10" s="9" t="s">
+      <c r="AP10" s="9" t="s">
         <v>606</v>
       </c>
-      <c r="AP10" s="9" t="s">
+      <c r="AQ10" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="AR10" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="AQ10" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="AR10" s="9" t="s">
+      <c r="AS10" s="9" t="s">
         <v>608</v>
       </c>
-      <c r="AS10" s="9" t="s">
+      <c r="AT10" s="9" t="s">
         <v>609</v>
-      </c>
-      <c r="AT10" s="9" t="s">
-        <v>610</v>
       </c>
       <c r="AU10" s="18">
         <v>0.32500000000000001</v>
@@ -5432,7 +5451,7 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="AW10" s="9" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AX10" s="9">
         <v>106</v>
@@ -5447,19 +5466,19 @@
         <v>0.45660000000000001</v>
       </c>
       <c r="BB10" s="9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="BC10" s="9">
         <v>14</v>
       </c>
       <c r="BD10" s="18" t="s">
+        <v>611</v>
+      </c>
+      <c r="BE10" s="9" t="s">
         <v>612</v>
       </c>
-      <c r="BE10" s="9" t="s">
+      <c r="BF10" s="11" t="s">
         <v>613</v>
-      </c>
-      <c r="BF10" s="11" t="s">
-        <v>614</v>
       </c>
       <c r="BG10" s="19">
         <v>0.91</v>
@@ -5468,16 +5487,16 @@
         <v>98</v>
       </c>
       <c r="BI10" s="9" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="BJ10" s="9">
         <v>1030.74</v>
       </c>
       <c r="BK10" s="9" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="BL10" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BR10" s="9" t="s">
         <v>134</v>
@@ -5491,17 +5510,17 @@
         <v>409</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D11" s="12" t="str">
         <f t="shared" si="5"/>
         <v>413 頤昌璞岳</v>
       </c>
       <c r="E11" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>583</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>584</v>
       </c>
       <c r="G11" s="14">
         <v>27.11</v>
@@ -5509,7 +5528,9 @@
       <c r="H11" s="13">
         <v>26.83</v>
       </c>
-      <c r="I11" s="13"/>
+      <c r="I11" s="13">
+        <v>124</v>
+      </c>
       <c r="J11" s="14">
         <v>34.42</v>
       </c>
@@ -5517,7 +5538,7 @@
         <v>24.79</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="M11" s="15">
         <v>32</v>
@@ -5534,7 +5555,7 @@
         <v>0.5</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="R11" s="15">
         <v>32</v>
@@ -5557,22 +5578,22 @@
         <v>96</v>
       </c>
       <c r="AD11" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="AE11" s="9" t="s">
         <v>586</v>
-      </c>
-      <c r="AE11" s="9" t="s">
-        <v>587</v>
       </c>
       <c r="AF11" s="10">
         <v>2022</v>
       </c>
       <c r="AG11" s="9" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AH11" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AI11" s="9" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AJ11" s="9" t="s">
         <v>171</v>
@@ -5581,31 +5602,31 @@
         <v>83</v>
       </c>
       <c r="AL11" s="9" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AM11" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="AN11" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="AN11" s="9" t="s">
+      <c r="AO11" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="AP11" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="AQ11" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="AR11" s="9" t="s">
         <v>591</v>
       </c>
-      <c r="AO11" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="AP11" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="AQ11" s="9" t="s">
-        <v>497</v>
-      </c>
-      <c r="AR11" s="9" t="s">
+      <c r="AS11" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="AT11" s="9" t="s">
         <v>592</v>
-      </c>
-      <c r="AS11" s="9" t="s">
-        <v>499</v>
-      </c>
-      <c r="AT11" s="9" t="s">
-        <v>593</v>
       </c>
       <c r="AU11" s="18">
         <v>0.32100000000000001</v>
@@ -5614,7 +5635,7 @@
         <v>0.32100000000000001</v>
       </c>
       <c r="AW11" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AX11" s="9">
         <v>124</v>
@@ -5629,13 +5650,13 @@
         <v>0.51349999999999996</v>
       </c>
       <c r="BB11" s="20" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="BC11" s="20">
         <v>14</v>
       </c>
       <c r="BD11" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="BE11" s="9" t="s">
         <v>182</v>
@@ -5650,7 +5671,7 @@
         <v>98</v>
       </c>
       <c r="BI11" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="BJ11" s="9">
         <v>595.29</v>
@@ -5659,7 +5680,7 @@
         <v>100</v>
       </c>
       <c r="BL11" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BM11" s="9" t="s">
         <v>102</v>
@@ -5668,10 +5689,10 @@
         <v>102</v>
       </c>
       <c r="BO11" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="BP11" s="9" t="s">
         <v>598</v>
-      </c>
-      <c r="BP11" s="9" t="s">
-        <v>599</v>
       </c>
       <c r="BQ11" s="9" t="s">
         <v>102</v>
@@ -5707,7 +5728,7 @@
         <v>73</v>
       </c>
       <c r="I12" s="13">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="J12" s="14">
         <v>32.01</v>
@@ -6113,7 +6134,7 @@
         <v>454</v>
       </c>
       <c r="I14" s="22">
-        <v>130</v>
+        <v>356</v>
       </c>
       <c r="J14" s="21">
         <v>31.65</v>
@@ -6296,20 +6317,20 @@
         <v>505</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D15" s="12" t="str">
         <f t="shared" si="5"/>
         <v>505 櫻花澍</v>
       </c>
       <c r="E15" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="F15" s="20" t="s">
         <v>697</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>698</v>
       </c>
       <c r="G15" s="21">
         <v>26.2</v>
@@ -6317,7 +6338,9 @@
       <c r="H15" s="22">
         <v>26.09</v>
       </c>
-      <c r="I15" s="22"/>
+      <c r="I15" s="22">
+        <v>120</v>
+      </c>
       <c r="J15" s="21">
         <v>28.35</v>
       </c>
@@ -6325,7 +6348,7 @@
         <v>24.04</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="M15" s="15">
         <v>28</v>
@@ -6342,7 +6365,7 @@
         <v>2</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="R15" s="15">
         <v>28</v>
@@ -6362,13 +6385,13 @@
         <v>135</v>
       </c>
       <c r="W15" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="X15" s="20" t="s">
         <v>700</v>
       </c>
-      <c r="X15" s="20" t="s">
+      <c r="Z15" s="9" t="s">
         <v>701</v>
-      </c>
-      <c r="Z15" s="9" t="s">
-        <v>702</v>
       </c>
       <c r="AA15" s="16">
         <v>165</v>
@@ -6380,7 +6403,7 @@
         <v>112</v>
       </c>
       <c r="AD15" s="9" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AE15" s="9" t="s">
         <v>458</v>
@@ -6395,7 +6418,7 @@
         <v>80</v>
       </c>
       <c r="AI15" s="9" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AJ15" s="9" t="s">
         <v>171</v>
@@ -6407,28 +6430,28 @@
         <v>117</v>
       </c>
       <c r="AM15" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="AN15" s="9" t="s">
         <v>704</v>
       </c>
-      <c r="AN15" s="9" t="s">
+      <c r="AO15" s="9" t="s">
         <v>705</v>
       </c>
-      <c r="AO15" s="9" t="s">
+      <c r="AP15" s="9" t="s">
         <v>706</v>
       </c>
-      <c r="AP15" s="9" t="s">
-        <v>707</v>
-      </c>
       <c r="AQ15" s="9" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AR15" s="9" t="s">
         <v>90</v>
       </c>
       <c r="AS15" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="AT15" s="9" t="s">
         <v>708</v>
-      </c>
-      <c r="AT15" s="9" t="s">
-        <v>709</v>
       </c>
       <c r="AU15" s="17">
         <v>0.32</v>
@@ -6437,7 +6460,7 @@
         <v>0.32</v>
       </c>
       <c r="AW15" s="9" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AX15" s="9">
         <v>106</v>
@@ -6452,16 +6475,16 @@
         <v>0.38140000000000002</v>
       </c>
       <c r="BB15" s="9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="BC15" s="9">
         <v>14</v>
       </c>
       <c r="BD15" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="BE15" s="9" t="s">
         <v>711</v>
-      </c>
-      <c r="BE15" s="9" t="s">
-        <v>712</v>
       </c>
       <c r="BF15" s="11" t="s">
         <v>138</v>
@@ -6473,7 +6496,7 @@
         <v>98</v>
       </c>
       <c r="BI15" s="9" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="BJ15" s="9">
         <v>602.07000000000005</v>
@@ -6482,13 +6505,13 @@
         <v>100</v>
       </c>
       <c r="BL15" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BN15" s="9" t="s">
         <v>102</v>
       </c>
       <c r="BO15" s="9" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="BP15" s="9" t="s">
         <v>470</v>
@@ -6497,7 +6520,7 @@
         <v>102</v>
       </c>
       <c r="BR15" s="9" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="16" spans="1:70" ht="16">
@@ -6524,7 +6547,9 @@
       <c r="H16" s="13">
         <v>22.46</v>
       </c>
-      <c r="I16" s="13"/>
+      <c r="I16" s="13">
+        <v>270</v>
+      </c>
       <c r="J16" s="14">
         <v>28.11</v>
       </c>
@@ -6915,28 +6940,30 @@
         <v>502</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D18" s="12" t="str">
         <f t="shared" si="5"/>
         <v>502 富宇天匯</v>
       </c>
       <c r="E18" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="F18" s="20" t="s">
         <v>676</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>677</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
+      <c r="I18" s="22">
+        <v>192</v>
+      </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
       <c r="L18" s="9" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="M18" s="15">
         <v>39</v>
@@ -6953,7 +6980,7 @@
         <v>2</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="R18" s="15">
         <v>45</v>
@@ -6970,7 +6997,7 @@
         <v>47.5</v>
       </c>
       <c r="Z18" s="9" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AA18" s="16">
         <v>160</v>
@@ -6985,19 +7012,19 @@
         <v>77</v>
       </c>
       <c r="AE18" s="9" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="AF18" s="10">
         <v>2023</v>
       </c>
       <c r="AG18" s="9" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AH18" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AI18" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="AJ18" s="9" t="s">
         <v>171</v>
@@ -7009,25 +7036,25 @@
         <v>117</v>
       </c>
       <c r="AM18" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="AN18" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="AN18" s="9" t="s">
+      <c r="AO18" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="AO18" s="9" t="s">
+      <c r="AP18" s="9" t="s">
         <v>686</v>
-      </c>
-      <c r="AP18" s="9" t="s">
-        <v>687</v>
       </c>
       <c r="AQ18" s="9" t="s">
         <v>202</v>
       </c>
       <c r="AR18" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="AS18" s="9" t="s">
         <v>688</v>
-      </c>
-      <c r="AS18" s="9" t="s">
-        <v>689</v>
       </c>
       <c r="AT18" s="9" t="s">
         <v>386</v>
@@ -7039,7 +7066,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="AW18" s="9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AX18" s="9">
         <v>266</v>
@@ -7060,13 +7087,13 @@
         <v>15</v>
       </c>
       <c r="BD18" s="18" t="s">
+        <v>690</v>
+      </c>
+      <c r="BE18" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="BF18" s="11" t="s">
         <v>691</v>
-      </c>
-      <c r="BE18" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="BF18" s="11" t="s">
-        <v>692</v>
       </c>
       <c r="BG18" s="19">
         <v>1.03</v>
@@ -7075,7 +7102,7 @@
         <v>98</v>
       </c>
       <c r="BI18" s="9" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="BJ18" s="9">
         <v>1471.38</v>
@@ -7084,7 +7111,7 @@
         <v>100</v>
       </c>
       <c r="BL18" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="BM18" s="9" t="s">
         <v>102</v>
@@ -7093,16 +7120,16 @@
         <v>102</v>
       </c>
       <c r="BO18" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="BP18" s="9" t="s">
         <v>694</v>
-      </c>
-      <c r="BP18" s="9" t="s">
-        <v>695</v>
       </c>
       <c r="BQ18" s="9" t="s">
         <v>102</v>
       </c>
       <c r="BR18" s="9" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="19" spans="1:70">
@@ -7129,8 +7156,8 @@
       <c r="H19" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="I19" s="13">
-        <v>154</v>
+      <c r="I19" s="13" t="s">
+        <v>752</v>
       </c>
       <c r="J19" s="14">
         <v>28.96</v>
@@ -7319,26 +7346,26 @@
         <v>297</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D20" s="12" t="str">
         <f t="shared" si="5"/>
         <v>313 大亮時代A7</v>
       </c>
       <c r="E20" s="12" t="s">
+        <v>617</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>618</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>619</v>
       </c>
       <c r="G20" s="14">
         <v>29.4</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I20" s="13">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="J20" s="14">
         <v>34.24</v>
@@ -7347,7 +7374,7 @@
         <v>27.17</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="M20" s="15">
         <v>35</v>
@@ -7364,7 +7391,7 @@
         <v>0.5</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="R20" s="15">
         <v>35</v>
@@ -7381,7 +7408,7 @@
         <v>35.5</v>
       </c>
       <c r="Z20" s="9" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AA20" s="16">
         <v>148</v>
@@ -7396,7 +7423,7 @@
         <v>77</v>
       </c>
       <c r="AE20" s="9" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AF20" s="10">
         <v>2023</v>
@@ -7408,7 +7435,7 @@
         <v>80</v>
       </c>
       <c r="AI20" s="9" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AJ20" s="9" t="s">
         <v>171</v>
@@ -7417,31 +7444,31 @@
         <v>83</v>
       </c>
       <c r="AL20" s="9" t="s">
+        <v>624</v>
+      </c>
+      <c r="AM20" s="9" t="s">
         <v>625</v>
       </c>
-      <c r="AM20" s="9" t="s">
+      <c r="AN20" s="9" t="s">
         <v>626</v>
       </c>
-      <c r="AN20" s="9" t="s">
+      <c r="AO20" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="AO20" s="9" t="s">
+      <c r="AP20" s="9" t="s">
         <v>628</v>
       </c>
-      <c r="AP20" s="9" t="s">
+      <c r="AQ20" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="AR20" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="AQ20" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="AR20" s="9" t="s">
+      <c r="AS20" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="AT20" s="9" t="s">
         <v>630</v>
-      </c>
-      <c r="AS20" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="AT20" s="9" t="s">
-        <v>631</v>
       </c>
       <c r="AU20" s="18">
         <v>0.33900000000000002</v>
@@ -7450,7 +7477,7 @@
         <v>0.33900000000000002</v>
       </c>
       <c r="AW20" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AX20" s="9">
         <v>87</v>
@@ -7471,13 +7498,13 @@
         <v>15</v>
       </c>
       <c r="BD20" s="18" t="s">
+        <v>632</v>
+      </c>
+      <c r="BE20" s="9" t="s">
         <v>633</v>
       </c>
-      <c r="BE20" s="9" t="s">
+      <c r="BF20" s="11" t="s">
         <v>634</v>
-      </c>
-      <c r="BF20" s="11" t="s">
-        <v>635</v>
       </c>
       <c r="BG20" s="19">
         <v>0.36</v>
@@ -7486,7 +7513,7 @@
         <v>98</v>
       </c>
       <c r="BI20" s="9" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="BJ20" s="9">
         <v>332.5</v>
@@ -7498,10 +7525,10 @@
         <v>318</v>
       </c>
       <c r="BO20" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="BP20" s="9" t="s">
         <v>637</v>
-      </c>
-      <c r="BP20" s="9" t="s">
-        <v>638</v>
       </c>
       <c r="BQ20" s="9" t="s">
         <v>102</v>
@@ -7537,7 +7564,7 @@
         <v>476</v>
       </c>
       <c r="I21" s="13">
-        <v>89</v>
+        <v>447</v>
       </c>
       <c r="J21" s="14">
         <v>41.77</v>
@@ -7723,17 +7750,17 @@
         <v>409</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D22" s="12" t="str">
         <f t="shared" si="5"/>
         <v>410 新未來3</v>
       </c>
       <c r="E22" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="F22" s="20" t="s">
         <v>527</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>528</v>
       </c>
       <c r="G22" s="21">
         <v>30.02</v>
@@ -7741,7 +7768,9 @@
       <c r="H22" s="22">
         <v>29.48</v>
       </c>
-      <c r="I22" s="22"/>
+      <c r="I22" s="22">
+        <v>66</v>
+      </c>
       <c r="J22" s="21">
         <v>32</v>
       </c>
@@ -7749,7 +7778,7 @@
         <v>25.65</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M22" s="15">
         <v>33</v>
@@ -7766,7 +7795,7 @@
         <v>2.5</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R22" s="15">
         <v>33</v>
@@ -7783,7 +7812,7 @@
         <v>35.5</v>
       </c>
       <c r="Z22" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AA22" s="16">
         <v>190</v>
@@ -7798,7 +7827,7 @@
         <v>77</v>
       </c>
       <c r="AE22" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AF22" s="10">
         <v>2023</v>
@@ -7810,7 +7839,7 @@
         <v>80</v>
       </c>
       <c r="AI22" s="9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AJ22" s="9" t="s">
         <v>171</v>
@@ -7822,25 +7851,25 @@
         <v>117</v>
       </c>
       <c r="AM22" s="9" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AN22" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="AO22" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="AO22" s="9" t="s">
+      <c r="AP22" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="AP22" s="9" t="s">
+      <c r="AQ22" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="AR22" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="AQ22" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="AR22" s="9" t="s">
+      <c r="AS22" s="9" t="s">
         <v>519</v>
-      </c>
-      <c r="AS22" s="9" t="s">
-        <v>520</v>
       </c>
       <c r="AT22" s="9" t="s">
         <v>465</v>
@@ -7852,7 +7881,7 @@
         <v>0.3327</v>
       </c>
       <c r="AW22" s="9" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AX22" s="9">
         <v>582</v>
@@ -7867,13 +7896,13 @@
         <v>0.38300000000000001</v>
       </c>
       <c r="BB22" s="9" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="BC22" s="9">
         <v>22</v>
       </c>
       <c r="BD22" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="BE22" s="9" t="s">
         <v>182</v>
@@ -7888,7 +7917,7 @@
         <v>98</v>
       </c>
       <c r="BI22" s="9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="BJ22" s="9">
         <v>2513.2199999999998</v>
@@ -7906,10 +7935,10 @@
         <v>102</v>
       </c>
       <c r="BO22" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="BP22" s="9" t="s">
         <v>538</v>
-      </c>
-      <c r="BP22" s="9" t="s">
-        <v>539</v>
       </c>
       <c r="BQ22" s="9" t="s">
         <v>102</v>
@@ -7945,7 +7974,7 @@
         <v>391</v>
       </c>
       <c r="I23" s="22">
-        <v>634</v>
+        <v>745</v>
       </c>
       <c r="J23" s="21">
         <v>31.03</v>
@@ -8128,22 +8157,24 @@
         <v>409</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D24" s="12" t="str">
         <f t="shared" si="5"/>
         <v>417 頤昌澄岳</v>
       </c>
       <c r="E24" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="F24" s="20" t="s">
         <v>661</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>662</v>
       </c>
       <c r="H24" s="22">
         <v>25.41</v>
       </c>
-      <c r="I24" s="22"/>
+      <c r="I24" s="22" t="s">
+        <v>753</v>
+      </c>
       <c r="J24" s="19">
         <v>25.92</v>
       </c>
@@ -8151,7 +8182,7 @@
         <v>25.06</v>
       </c>
       <c r="Q24" s="15" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="R24" s="15">
         <v>39</v>
@@ -8164,7 +8195,7 @@
         <v>39.5</v>
       </c>
       <c r="Z24" s="9" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AA24" s="16">
         <v>175</v>
@@ -8188,7 +8219,7 @@
         <v>80</v>
       </c>
       <c r="AI24" s="9" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AJ24" s="9" t="s">
         <v>171</v>
@@ -8200,22 +8231,22 @@
         <v>172</v>
       </c>
       <c r="AM24" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="AN24" s="9" t="s">
         <v>666</v>
       </c>
-      <c r="AN24" s="9" t="s">
-        <v>667</v>
-      </c>
       <c r="AO24" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="AP24" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="AP24" s="9" t="s">
-        <v>497</v>
-      </c>
       <c r="AQ24" s="9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AR24" s="9" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AS24" s="9" t="s">
         <v>245</v>
@@ -8227,7 +8258,7 @@
         <v>0.33</v>
       </c>
       <c r="AW24" s="9" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AX24" s="9">
         <v>140</v>
@@ -8248,13 +8279,13 @@
         <v>15</v>
       </c>
       <c r="BD24" s="9" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="BE24" s="9" t="s">
         <v>182</v>
       </c>
       <c r="BF24" s="11" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="BG24" s="19">
         <v>0.97</v>
@@ -8263,7 +8294,7 @@
         <v>184</v>
       </c>
       <c r="BI24" s="9" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="BJ24" s="19">
         <v>665.31</v>
@@ -8275,10 +8306,10 @@
         <v>247</v>
       </c>
       <c r="BO24" s="9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="BP24" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="BR24" s="9" t="s">
         <v>134</v>
@@ -8292,26 +8323,26 @@
         <v>409</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D25" s="12" t="str">
         <f t="shared" si="5"/>
         <v>416 維特魯威</v>
       </c>
       <c r="E25" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="F25" s="20" t="s">
         <v>640</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>641</v>
       </c>
       <c r="G25" s="19">
         <v>31.65</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="I25" s="9">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J25" s="19">
         <v>38.68</v>
@@ -8320,7 +8351,7 @@
         <v>27.48</v>
       </c>
       <c r="Q25" s="15" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="R25" s="15">
         <v>37.799999999999997</v>
@@ -8336,19 +8367,19 @@
         <v>77</v>
       </c>
       <c r="AE25" s="9" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AF25" s="10">
         <v>2024</v>
       </c>
       <c r="AG25" s="9" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AH25" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AI25" s="9" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AJ25" s="9" t="s">
         <v>171</v>
@@ -8360,25 +8391,25 @@
         <v>172</v>
       </c>
       <c r="AM25" s="9" t="s">
+        <v>646</v>
+      </c>
+      <c r="AN25" s="9" t="s">
         <v>647</v>
       </c>
-      <c r="AN25" s="9" t="s">
+      <c r="AO25" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="AO25" s="9" t="s">
+      <c r="AP25" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="AP25" s="9" t="s">
+      <c r="AQ25" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="AR25" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="AQ25" s="9" t="s">
-        <v>650</v>
-      </c>
-      <c r="AR25" s="9" t="s">
+      <c r="AS25" s="9" t="s">
         <v>651</v>
-      </c>
-      <c r="AS25" s="9" t="s">
-        <v>652</v>
       </c>
       <c r="AU25" s="18">
         <v>0.33400000000000002</v>
@@ -8387,7 +8418,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="AW25" s="9" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AX25" s="9">
         <v>123</v>
@@ -8402,19 +8433,19 @@
         <v>0.37569999999999998</v>
       </c>
       <c r="BB25" s="9" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="BC25" s="9">
         <v>28</v>
       </c>
       <c r="BD25" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="BE25" s="9" t="s">
         <v>655</v>
       </c>
-      <c r="BE25" s="9" t="s">
+      <c r="BF25" s="11" t="s">
         <v>656</v>
-      </c>
-      <c r="BF25" s="11" t="s">
-        <v>657</v>
       </c>
       <c r="BG25" s="19">
         <v>1.02</v>
@@ -8423,7 +8454,7 @@
         <v>184</v>
       </c>
       <c r="BI25" s="9" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="BJ25" s="19">
         <v>586.6</v>
@@ -8435,7 +8466,7 @@
         <v>272</v>
       </c>
       <c r="BO25" s="9" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="BP25" s="9" t="s">
         <v>248</v>
@@ -8466,7 +8497,9 @@
       </c>
       <c r="G26" s="14"/>
       <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
+      <c r="I26" s="13">
+        <v>470</v>
+      </c>
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="9" t="s">
@@ -8666,7 +8699,7 @@
         <v>220</v>
       </c>
       <c r="I27" s="13">
-        <v>929</v>
+        <v>961</v>
       </c>
       <c r="J27" s="14">
         <v>37.450000000000003</v>
@@ -8866,7 +8899,9 @@
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
+      <c r="I28" s="22">
+        <v>416</v>
+      </c>
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
       <c r="L28" s="9" t="s">
@@ -9054,7 +9089,7 @@
         <v>108 豐邑氧森</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>164</v>
@@ -9230,7 +9265,9 @@
       </c>
       <c r="G30" s="14"/>
       <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
+      <c r="I30" s="13">
+        <v>628</v>
+      </c>
       <c r="J30" s="14"/>
       <c r="K30" s="14"/>
       <c r="L30" s="9" t="s">
@@ -9411,26 +9448,26 @@
         <v>409</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D31" s="12" t="str">
         <f t="shared" si="5"/>
         <v>418 玄泰T1</v>
       </c>
       <c r="E31" s="12" t="s">
+        <v>716</v>
+      </c>
+      <c r="F31" s="20" t="s">
         <v>717</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>718</v>
       </c>
       <c r="G31" s="19">
         <v>27.3</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="I31" s="22">
-        <v>378</v>
+        <v>401</v>
       </c>
       <c r="J31" s="19">
         <v>36.26</v>
@@ -9439,7 +9476,7 @@
         <v>21.25</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="R31" s="15">
         <v>34</v>
@@ -9451,7 +9488,7 @@
         <v>36</v>
       </c>
       <c r="Z31" s="9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AA31" s="16">
         <v>160</v>
@@ -9463,19 +9500,19 @@
         <v>77</v>
       </c>
       <c r="AE31" s="9" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AF31" s="10">
         <v>2026</v>
       </c>
       <c r="AG31" s="9" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AH31" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AI31" s="9" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AJ31" s="9" t="s">
         <v>171</v>
@@ -9487,25 +9524,25 @@
         <v>172</v>
       </c>
       <c r="AM31" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="AN31" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="AN31" s="9" t="s">
+      <c r="AO31" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="AO31" s="9" t="s">
+      <c r="AP31" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="AP31" s="9" t="s">
+      <c r="AQ31" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="AR31" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="AQ31" s="9" t="s">
-        <v>728</v>
-      </c>
-      <c r="AR31" s="9" t="s">
+      <c r="AS31" s="9" t="s">
         <v>729</v>
-      </c>
-      <c r="AS31" s="9" t="s">
-        <v>730</v>
       </c>
       <c r="AU31" s="18">
         <v>0.33</v>
@@ -9514,7 +9551,7 @@
         <v>0.33</v>
       </c>
       <c r="AW31" s="9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AX31" s="9">
         <v>264</v>
@@ -9529,13 +9566,13 @@
         <v>0.59189999999999998</v>
       </c>
       <c r="BB31" s="9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="BC31" s="9">
         <v>25</v>
       </c>
       <c r="BD31" s="9" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="BE31" s="9" t="s">
         <v>316</v>
@@ -9550,7 +9587,7 @@
         <v>184</v>
       </c>
       <c r="BI31" s="9" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="BJ31" s="19">
         <v>1848.19</v>
@@ -9562,7 +9599,7 @@
         <v>272</v>
       </c>
       <c r="BO31" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="BR31" s="9" t="s">
         <v>134</v>
@@ -9576,23 +9613,23 @@
         <v>297</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D32" s="12" t="str">
         <f t="shared" si="5"/>
         <v>314 大亮 泊</v>
       </c>
       <c r="E32" s="12" t="s">
+        <v>736</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>737</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>738</v>
       </c>
       <c r="G32" s="14">
         <v>33.700000000000003</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="I32" s="13">
         <v>610</v>
@@ -9600,7 +9637,7 @@
       <c r="J32" s="14"/>
       <c r="K32" s="14"/>
       <c r="Q32" s="9" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="R32" s="15">
         <v>38</v>
@@ -9617,7 +9654,7 @@
         <v>39</v>
       </c>
       <c r="Z32" s="9" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AA32" s="16">
         <v>185</v>
@@ -9632,19 +9669,19 @@
         <v>77</v>
       </c>
       <c r="AE32" s="9" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AF32" s="10">
         <v>2026</v>
       </c>
       <c r="AG32" s="9" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AH32" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AI32" s="27" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AJ32" s="9" t="s">
         <v>171</v>
@@ -9653,25 +9690,25 @@
         <v>83</v>
       </c>
       <c r="AL32" s="9" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AM32" s="9" t="s">
         <v>244</v>
       </c>
       <c r="AN32" s="9" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AP32" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="AQ32" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="AR32" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="AQ32" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="AR32" s="9" t="s">
-        <v>630</v>
-      </c>
       <c r="AS32" s="9" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AU32" s="18">
         <v>0.33900000000000002</v>
@@ -9680,7 +9717,7 @@
         <v>0.33900000000000002</v>
       </c>
       <c r="AW32" s="27" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AX32" s="9">
         <v>568</v>
@@ -9695,19 +9732,19 @@
         <v>0.63100000000000001</v>
       </c>
       <c r="BB32" s="9" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="BC32" s="9">
         <v>29</v>
       </c>
       <c r="BD32" s="18" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="BE32" s="9" t="s">
         <v>246</v>
       </c>
       <c r="BF32" s="11" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="BG32" s="19">
         <v>0.56000000000000005</v>
@@ -9716,7 +9753,7 @@
         <v>184</v>
       </c>
       <c r="BI32" s="9" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="BJ32" s="9">
         <v>2214</v>

--- a/db/A7XLK-1111-HouseApp3.xlsx
+++ b/db/A7XLK-1111-HouseApp3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CC8D1E-9C0B-1F4F-A29A-7191CE23D7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B18926-C8D1-704C-9892-FC2D7D29F0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="980" yWindow="-18340" windowWidth="27320" windowHeight="16380" xr2:uid="{33D194D6-A429-7949-A97B-0894189945E2}"/>
+    <workbookView xWindow="-5100" yWindow="-20300" windowWidth="27320" windowHeight="16380" xr2:uid="{33D194D6-A429-7949-A97B-0894189945E2}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="753">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -58,10 +58,6 @@
   <si>
     <t>Link</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>實價2021</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>實價總平均或登錄筆數</t>
@@ -2979,11 +2975,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>完售</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>實價2022</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3514,196 +3510,196 @@
         <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="7" t="s">
+      <c r="AP1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AV1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="8" t="s">
+      <c r="AW1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="BA1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="8" t="s">
+      <c r="BB1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BC1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="3" t="s">
+      <c r="BD1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="3" t="s">
+      <c r="BE1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BF1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BG1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" s="4" t="s">
+      <c r="BH1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BI1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" s="3" t="s">
+      <c r="BJ1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="BJ1" s="4" t="s">
+      <c r="BK1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" s="3" t="s">
+      <c r="BL1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="BL1" s="3" t="s">
+      <c r="BM1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" s="3" t="s">
+      <c r="BN1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" s="3" t="s">
+      <c r="BO1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="BO1" s="3" t="s">
+      <c r="BP1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="BP1" s="3" t="s">
+      <c r="BQ1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" s="3" t="s">
+      <c r="BR1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="BR1" s="3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:70">
@@ -3711,23 +3707,23 @@
         <v>102</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D2" s="12" t="str">
         <f t="shared" ref="D2:D9" si="0">CONCATENATE(A2," ",C2)</f>
         <v>102 鴻典</v>
       </c>
       <c r="E2" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>108</v>
-      </c>
       <c r="G2" s="14">
-        <v>24.35</v>
+        <v>24.8</v>
       </c>
       <c r="H2" s="13">
         <v>23.38</v>
@@ -3742,7 +3738,7 @@
         <v>20.440000000000001</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M2" s="15">
         <v>26</v>
@@ -3759,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="R2" s="15">
         <v>29</v>
@@ -3776,7 +3772,7 @@
         <v>29</v>
       </c>
       <c r="Z2" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AA2" s="16">
         <v>180</v>
@@ -3785,67 +3781,67 @@
         <v>210</v>
       </c>
       <c r="AC2" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD2" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE2" s="9" t="s">
         <v>112</v>
-      </c>
-      <c r="AD2" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE2" s="9" t="s">
-        <v>113</v>
       </c>
       <c r="AF2" s="10">
         <v>2022</v>
       </c>
       <c r="AG2" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AH2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI2" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="AH2" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI2" s="9" t="s">
+      <c r="AJ2" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="AJ2" s="9" t="s">
+      <c r="AK2" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL2" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="AK2" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL2" s="9" t="s">
+      <c r="AM2" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="AM2" s="9" t="s">
+      <c r="AN2" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AO2" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="AN2" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="AO2" s="9" t="s">
+      <c r="AP2" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="AP2" s="9" t="s">
+      <c r="AQ2" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR2" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="AQ2" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR2" s="9" t="s">
+      <c r="AS2" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="AS2" s="9" t="s">
+      <c r="AT2" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="AT2" s="9" t="s">
+      <c r="AU2" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="AU2" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="AV2" s="18">
         <v>0.32</v>
       </c>
       <c r="AW2" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AX2" s="9">
         <v>196</v>
@@ -3854,61 +3850,61 @@
         <v>11</v>
       </c>
       <c r="AZ2" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BA2" s="18">
         <v>0.39800000000000002</v>
       </c>
       <c r="BB2" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BC2" s="9">
         <v>15</v>
       </c>
       <c r="BD2" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="BE2" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="BE2" s="9" t="s">
+      <c r="BF2" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="BF2" s="11" t="s">
-        <v>130</v>
       </c>
       <c r="BG2" s="19">
         <v>1.03</v>
       </c>
       <c r="BH2" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI2" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BJ2" s="9">
         <v>1062.93</v>
       </c>
       <c r="BK2" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="BL2" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="BL2" s="9" t="s">
+      <c r="BM2" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="BM2" s="9" t="s">
-        <v>102</v>
-      </c>
       <c r="BN2" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO2" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="BP2" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="BP2" s="9" t="s">
+      <c r="BQ2" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BR2" s="9" t="s">
         <v>133</v>
-      </c>
-      <c r="BQ2" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BR2" s="9" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:70">
@@ -3916,26 +3912,26 @@
         <v>105</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D3" s="12" t="str">
         <f t="shared" si="0"/>
         <v>105 樂田田</v>
       </c>
       <c r="E3" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F3" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="G3" s="21">
+        <v>23</v>
+      </c>
+      <c r="H3" s="22" t="s">
         <v>141</v>
-      </c>
-      <c r="G3" s="21">
-        <v>22.84</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>142</v>
       </c>
       <c r="I3" s="22">
         <v>221</v>
@@ -3947,7 +3943,7 @@
         <v>19.62</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M3" s="15">
         <v>25</v>
@@ -3964,7 +3960,7 @@
         <v>0.5</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R3" s="15">
         <v>26</v>
@@ -3981,10 +3977,10 @@
         <v>26</v>
       </c>
       <c r="V3" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z3" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AA3" s="16">
         <v>190</v>
@@ -3996,55 +3992,55 @@
         <v>0.8</v>
       </c>
       <c r="AD3" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE3" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AF3" s="10">
         <v>2022</v>
       </c>
       <c r="AG3" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH3" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI3" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="AJ3" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK3" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL3" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM3" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="AJ3" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK3" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL3" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" s="9" t="s">
+      <c r="AN3" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="AN3" s="9" t="s">
+      <c r="AO3" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="AO3" s="9" t="s">
+      <c r="AP3" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="AP3" s="9" t="s">
+      <c r="AQ3" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR3" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="AQ3" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR3" s="9" t="s">
+      <c r="AS3" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="AS3" s="9" t="s">
+      <c r="AT3" s="9" t="s">
         <v>152</v>
-      </c>
-      <c r="AT3" s="9" t="s">
-        <v>153</v>
       </c>
       <c r="AU3" s="18">
         <v>0.32600000000000001</v>
@@ -4053,7 +4049,7 @@
         <v>0.32600000000000001</v>
       </c>
       <c r="AW3" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AX3" s="9">
         <v>187</v>
@@ -4068,55 +4064,55 @@
         <v>0.44269999999999998</v>
       </c>
       <c r="BB3" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BC3" s="9">
         <v>14</v>
       </c>
       <c r="BD3" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="BE3" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="BE3" s="9" t="s">
+      <c r="BF3" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="BF3" s="11" t="s">
-        <v>158</v>
       </c>
       <c r="BG3" s="19">
         <v>0.87</v>
       </c>
       <c r="BH3" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI3" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BJ3" s="9">
         <v>907.61</v>
       </c>
       <c r="BK3" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="BL3" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="BL3" s="9" t="s">
+      <c r="BM3" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="BM3" s="9" t="s">
-        <v>102</v>
-      </c>
       <c r="BN3" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO3" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="BP3" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="BP3" s="9" t="s">
-        <v>161</v>
-      </c>
       <c r="BQ3" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR3" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:70">
@@ -4124,23 +4120,23 @@
         <v>307</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D4" s="12" t="str">
         <f t="shared" si="0"/>
         <v>307 富宇悅峰</v>
       </c>
       <c r="E4" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>365</v>
-      </c>
       <c r="G4" s="14">
-        <v>24.96</v>
+        <v>25.7</v>
       </c>
       <c r="H4" s="13">
         <v>25.01</v>
@@ -4155,7 +4151,7 @@
         <v>23.49</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M4" s="15">
         <v>28</v>
@@ -4172,7 +4168,7 @@
         <v>2</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R4" s="15">
         <v>34</v>
@@ -4189,7 +4185,7 @@
         <v>35</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AA4" s="16">
         <v>175</v>
@@ -4198,67 +4194,67 @@
         <v>195</v>
       </c>
       <c r="AC4" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD4" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE4" s="9" t="s">
         <v>112</v>
-      </c>
-      <c r="AD4" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE4" s="9" t="s">
-        <v>113</v>
       </c>
       <c r="AF4" s="10">
         <v>2022</v>
       </c>
       <c r="AG4" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH4" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI4" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="AJ4" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK4" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL4" s="9" t="s">
         <v>368</v>
       </c>
-      <c r="AJ4" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK4" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL4" s="9" t="s">
+      <c r="AM4" s="9" t="s">
         <v>369</v>
       </c>
-      <c r="AM4" s="9" t="s">
+      <c r="AN4" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="AN4" s="9" t="s">
+      <c r="AO4" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="AP4" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="AQ4" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR4" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="AS4" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="AO4" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="AP4" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="AQ4" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="AR4" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="AS4" s="9" t="s">
+      <c r="AT4" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="AU4" s="9" t="s">
         <v>372</v>
-      </c>
-      <c r="AT4" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="AU4" s="9" t="s">
-        <v>373</v>
       </c>
       <c r="AV4" s="18">
         <v>0.36799999999999999</v>
       </c>
       <c r="AW4" s="9" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AX4" s="9">
         <v>264</v>
@@ -4267,61 +4263,61 @@
         <v>0</v>
       </c>
       <c r="AZ4" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="BA4" s="18">
         <v>0.40210000000000001</v>
       </c>
       <c r="BB4" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="BC4" s="9">
         <v>14</v>
       </c>
       <c r="BD4" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="BE4" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="BE4" s="9" t="s">
+      <c r="BF4" s="11" t="s">
         <v>378</v>
-      </c>
-      <c r="BF4" s="11" t="s">
-        <v>379</v>
       </c>
       <c r="BG4" s="19">
         <v>0.86</v>
       </c>
       <c r="BH4" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI4" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="BJ4" s="9">
         <v>1266.01</v>
       </c>
       <c r="BK4" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL4" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="BM4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN4" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO4" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="BP4" s="9" t="s">
         <v>381</v>
       </c>
-      <c r="BP4" s="9" t="s">
+      <c r="BQ4" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BR4" s="9" t="s">
         <v>382</v>
-      </c>
-      <c r="BQ4" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BR4" s="9" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:70" ht="21">
@@ -4329,22 +4325,24 @@
         <v>408</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D5" s="12" t="str">
         <f t="shared" si="0"/>
         <v>408 頤昌豐岳</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>751</v>
-      </c>
-      <c r="G5" s="21"/>
+        <v>750</v>
+      </c>
+      <c r="G5" s="21">
+        <v>25</v>
+      </c>
       <c r="H5" s="22">
         <v>24.99</v>
       </c>
@@ -4358,7 +4356,7 @@
         <v>22.52</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M5" s="15">
         <v>30</v>
@@ -4375,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="R5" s="15">
         <v>30</v>
@@ -4392,7 +4390,7 @@
         <v>30</v>
       </c>
       <c r="Z5" s="9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AA5" s="16">
         <v>160</v>
@@ -4401,58 +4399,58 @@
         <v>190</v>
       </c>
       <c r="AC5" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD5" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE5" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AF5" s="10">
         <v>2022</v>
       </c>
       <c r="AG5" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH5" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI5" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="AJ5" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK5" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL5" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM5" s="9" t="s">
         <v>493</v>
       </c>
-      <c r="AJ5" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK5" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL5" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM5" s="9" t="s">
+      <c r="AN5" s="26" t="s">
+        <v>493</v>
+      </c>
+      <c r="AO5" s="9" t="s">
         <v>494</v>
       </c>
-      <c r="AN5" s="26" t="s">
-        <v>494</v>
-      </c>
-      <c r="AO5" s="9" t="s">
+      <c r="AP5" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="AP5" s="9" t="s">
+      <c r="AQ5" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="AR5" s="9" t="s">
         <v>496</v>
       </c>
-      <c r="AQ5" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="AR5" s="9" t="s">
+      <c r="AS5" s="9" t="s">
         <v>497</v>
       </c>
-      <c r="AS5" s="9" t="s">
+      <c r="AT5" s="9" t="s">
         <v>498</v>
-      </c>
-      <c r="AT5" s="9" t="s">
-        <v>499</v>
       </c>
       <c r="AU5" s="17">
         <v>0.32</v>
@@ -4461,7 +4459,7 @@
         <v>0.32</v>
       </c>
       <c r="AW5" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AX5" s="9">
         <v>154</v>
@@ -4476,55 +4474,55 @@
         <v>0.4622</v>
       </c>
       <c r="BB5" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BC5" s="9">
         <v>15</v>
       </c>
       <c r="BD5" s="9" t="s">
+        <v>500</v>
+      </c>
+      <c r="BE5" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF5" s="11" t="s">
         <v>501</v>
-      </c>
-      <c r="BE5" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BF5" s="11" t="s">
-        <v>502</v>
       </c>
       <c r="BG5" s="19">
         <v>1.17</v>
       </c>
       <c r="BH5" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI5" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="BJ5" s="9">
         <v>933.78</v>
       </c>
       <c r="BK5" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL5" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="BM5" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BN5" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BO5" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="BM5" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BN5" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BO5" s="9" t="s">
+      <c r="BP5" s="9" t="s">
         <v>505</v>
       </c>
-      <c r="BP5" s="9" t="s">
-        <v>506</v>
-      </c>
       <c r="BQ5" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR5" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:70">
@@ -4532,26 +4530,26 @@
         <v>411</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>411 和洲金剛</v>
       </c>
       <c r="E6" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>540</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="G6" s="14">
+        <v>27.1</v>
+      </c>
+      <c r="H6" s="13" t="s">
         <v>541</v>
-      </c>
-      <c r="G6" s="14">
-        <v>26.33</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>542</v>
       </c>
       <c r="I6" s="13">
         <v>216</v>
@@ -4563,7 +4561,7 @@
         <v>21.01</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M6" s="15">
         <v>25</v>
@@ -4580,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="R6" s="15">
         <v>30</v>
@@ -4597,70 +4595,70 @@
         <v>31</v>
       </c>
       <c r="Z6" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC6" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD6" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE6" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AF6" s="10">
         <v>2022</v>
       </c>
       <c r="AG6" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AH6" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI6" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="AJ6" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK6" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL6" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM6" s="9" t="s">
         <v>544</v>
       </c>
-      <c r="AJ6" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK6" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL6" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM6" s="9" t="s">
+      <c r="AN6" s="9" t="s">
         <v>545</v>
       </c>
-      <c r="AN6" s="9" t="s">
+      <c r="AO6" s="9" t="s">
         <v>546</v>
       </c>
-      <c r="AO6" s="9" t="s">
+      <c r="AP6" s="9" t="s">
         <v>547</v>
       </c>
-      <c r="AP6" s="9" t="s">
+      <c r="AQ6" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR6" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="AS6" s="9" t="s">
         <v>548</v>
       </c>
-      <c r="AQ6" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR6" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="AS6" s="9" t="s">
-        <v>549</v>
-      </c>
       <c r="AT6" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AU6" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AV6" s="18">
         <v>0.32</v>
       </c>
       <c r="AW6" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AX6" s="9">
         <v>210</v>
@@ -4669,61 +4667,61 @@
         <v>11</v>
       </c>
       <c r="AZ6" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="BA6" s="18">
         <v>0.45540000000000003</v>
       </c>
       <c r="BB6" s="9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="BC6" s="9">
         <v>15</v>
       </c>
       <c r="BD6" s="9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="BE6" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="BF6" s="11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="BG6" s="19">
         <v>1.02</v>
       </c>
       <c r="BH6" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI6" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="BJ6" s="9">
         <v>1359.03</v>
       </c>
       <c r="BK6" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL6" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="BM6" s="9" t="s">
         <v>554</v>
       </c>
-      <c r="BM6" s="9" t="s">
+      <c r="BN6" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BO6" s="9" t="s">
         <v>555</v>
       </c>
-      <c r="BN6" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BO6" s="9" t="s">
-        <v>556</v>
-      </c>
       <c r="BP6" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="BQ6" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BR6" s="9" t="s">
         <v>133</v>
-      </c>
-      <c r="BQ6" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BR6" s="9" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:70" ht="16">
@@ -4731,26 +4729,26 @@
         <v>207</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>207 和耀恆美</v>
       </c>
       <c r="E7" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="G7" s="14">
+        <v>25.6</v>
+      </c>
+      <c r="H7" s="13" t="s">
         <v>277</v>
-      </c>
-      <c r="G7" s="14">
-        <v>25.24</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>278</v>
       </c>
       <c r="I7" s="13">
         <v>243</v>
@@ -4762,7 +4760,7 @@
         <v>21.86</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M7" s="15">
         <v>28</v>
@@ -4779,7 +4777,7 @@
         <v>2.5</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="R7" s="15">
         <v>35</v>
@@ -4796,70 +4794,70 @@
         <v>37.5</v>
       </c>
       <c r="Z7" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="AC7" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD7" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE7" s="9" t="s">
         <v>281</v>
-      </c>
-      <c r="AC7" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="AD7" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AE7" s="9" t="s">
-        <v>282</v>
       </c>
       <c r="AF7" s="10">
         <v>2022</v>
       </c>
       <c r="AG7" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="AH7" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI7" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="AH7" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI7" s="9" t="s">
+      <c r="AJ7" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK7" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL7" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM7" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="AJ7" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK7" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL7" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM7" s="9" t="s">
+      <c r="AN7" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="AN7" s="9" t="s">
+      <c r="AO7" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="AO7" s="9" t="s">
+      <c r="AP7" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="AP7" s="9" t="s">
+      <c r="AQ7" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR7" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS7" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="AQ7" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR7" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS7" s="9" t="s">
+      <c r="AT7" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="AT7" s="9" t="s">
+      <c r="AU7" s="9" t="s">
         <v>290</v>
-      </c>
-      <c r="AU7" s="9" t="s">
-        <v>291</v>
       </c>
       <c r="AV7" s="18">
         <v>0.32250000000000001</v>
       </c>
       <c r="AW7" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AX7" s="9">
         <v>280</v>
@@ -4874,52 +4872,52 @@
         <v>0.4743</v>
       </c>
       <c r="BB7" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BC7" s="9">
         <v>15</v>
       </c>
       <c r="BD7" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="BE7" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF7" s="11" t="s">
         <v>293</v>
-      </c>
-      <c r="BE7" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BF7" s="11" t="s">
-        <v>294</v>
       </c>
       <c r="BG7" s="19">
         <v>1.01</v>
       </c>
       <c r="BH7" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI7" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="BJ7" s="9">
         <v>1309.1400000000001</v>
       </c>
       <c r="BK7" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL7" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="BN7" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BO7" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="BP7" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="BN7" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BO7" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="BP7" s="9" t="s">
-        <v>248</v>
-      </c>
       <c r="BQ7" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR7" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:70">
@@ -4927,22 +4925,24 @@
         <v>409</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D8" s="12" t="str">
         <f t="shared" si="0"/>
         <v>409 新未來2</v>
       </c>
       <c r="E8" s="12" t="s">
+        <v>507</v>
+      </c>
+      <c r="F8" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="F8" s="20" t="s">
-        <v>509</v>
-      </c>
-      <c r="G8" s="21"/>
+      <c r="G8" s="21">
+        <v>26.5</v>
+      </c>
       <c r="H8" s="22">
         <v>26.39</v>
       </c>
@@ -4956,7 +4956,7 @@
         <v>23.12</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="M8" s="15">
         <v>30</v>
@@ -4973,7 +4973,7 @@
         <v>1</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R8" s="15">
         <v>30</v>
@@ -4990,7 +4990,7 @@
         <v>31</v>
       </c>
       <c r="Z8" s="9" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AA8" s="16">
         <v>180</v>
@@ -5002,55 +5002,55 @@
         <v>0.75</v>
       </c>
       <c r="AD8" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE8" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AF8" s="10">
         <v>2022</v>
       </c>
       <c r="AG8" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AH8" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI8" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="AJ8" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK8" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL8" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM8" s="9" t="s">
         <v>513</v>
       </c>
-      <c r="AJ8" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL8" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM8" s="9" t="s">
+      <c r="AN8" s="9" t="s">
         <v>514</v>
       </c>
-      <c r="AN8" s="9" t="s">
+      <c r="AO8" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="AO8" s="9" t="s">
+      <c r="AP8" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="AP8" s="9" t="s">
+      <c r="AQ8" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="AR8" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="AQ8" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="AR8" s="9" t="s">
+      <c r="AS8" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="AS8" s="9" t="s">
-        <v>519</v>
-      </c>
       <c r="AT8" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AU8" s="18">
         <v>0.33</v>
@@ -5059,7 +5059,7 @@
         <v>0.33</v>
       </c>
       <c r="AW8" s="9" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AX8" s="9">
         <v>376</v>
@@ -5074,55 +5074,55 @@
         <v>0.36220000000000002</v>
       </c>
       <c r="BB8" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="BC8" s="9">
         <v>22</v>
       </c>
       <c r="BD8" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="BE8" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="BF8" s="11" t="s">
         <v>182</v>
-      </c>
-      <c r="BF8" s="11" t="s">
-        <v>183</v>
       </c>
       <c r="BG8" s="19">
         <v>1.1399999999999999</v>
       </c>
       <c r="BH8" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI8" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="BJ8" s="9">
         <v>1955.56</v>
       </c>
       <c r="BK8" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL8" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BM8" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN8" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO8" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="BP8" s="9" t="s">
         <v>523</v>
       </c>
-      <c r="BP8" s="9" t="s">
-        <v>524</v>
-      </c>
       <c r="BQ8" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR8" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:70">
@@ -5130,26 +5130,26 @@
         <v>412</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>412 君邑丘比特</v>
       </c>
       <c r="E9" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>558</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="G9" s="14">
+        <v>28.4</v>
+      </c>
+      <c r="H9" s="13" t="s">
         <v>559</v>
-      </c>
-      <c r="G9" s="14">
-        <v>27.47</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>560</v>
       </c>
       <c r="I9" s="13">
         <v>183</v>
@@ -5161,7 +5161,7 @@
         <v>22.94</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="M9" s="15">
         <v>27.8</v>
@@ -5178,7 +5178,7 @@
         <v>2.1000000000000014</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="R9" s="15">
         <v>29.8</v>
@@ -5195,7 +5195,7 @@
         <v>34</v>
       </c>
       <c r="Z9" s="9" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AA9" s="16">
         <v>180</v>
@@ -5204,67 +5204,67 @@
         <v>230</v>
       </c>
       <c r="AC9" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD9" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE9" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AF9" s="10">
         <v>2022</v>
       </c>
       <c r="AG9" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AH9" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI9" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="AJ9" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK9" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL9" s="9" t="s">
         <v>565</v>
       </c>
-      <c r="AJ9" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK9" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL9" s="9" t="s">
+      <c r="AM9" s="9" t="s">
         <v>566</v>
       </c>
-      <c r="AM9" s="9" t="s">
+      <c r="AN9" s="9" t="s">
         <v>567</v>
       </c>
-      <c r="AN9" s="9" t="s">
+      <c r="AO9" s="9" t="s">
         <v>568</v>
       </c>
-      <c r="AO9" s="9" t="s">
+      <c r="AP9" s="9" t="s">
         <v>569</v>
       </c>
-      <c r="AP9" s="9" t="s">
+      <c r="AQ9" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="AR9" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="AQ9" s="9" t="s">
+      <c r="AS9" s="9" t="s">
         <v>570</v>
       </c>
-      <c r="AR9" s="9" t="s">
+      <c r="AT9" s="9" t="s">
         <v>571</v>
       </c>
-      <c r="AS9" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="AT9" s="9" t="s">
+      <c r="AU9" s="9" t="s">
         <v>572</v>
-      </c>
-      <c r="AU9" s="9" t="s">
-        <v>573</v>
       </c>
       <c r="AV9" s="18">
         <v>0.33129999999999998</v>
       </c>
       <c r="AW9" s="9" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AX9" s="9">
         <v>173</v>
@@ -5279,55 +5279,55 @@
         <v>0.46150000000000002</v>
       </c>
       <c r="BB9" s="9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="BC9" s="9">
         <v>15</v>
       </c>
       <c r="BD9" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="BE9" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF9" s="11" t="s">
         <v>576</v>
-      </c>
-      <c r="BE9" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BF9" s="11" t="s">
-        <v>577</v>
       </c>
       <c r="BG9" s="19">
         <v>1.07</v>
       </c>
       <c r="BH9" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI9" s="9" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="BJ9" s="9">
         <v>1030.74</v>
       </c>
       <c r="BK9" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL9" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="BM9" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN9" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO9" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="BP9" s="9" t="s">
         <v>579</v>
       </c>
-      <c r="BP9" s="9" t="s">
-        <v>580</v>
-      </c>
       <c r="BQ9" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR9" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:70">
@@ -5335,26 +5335,29 @@
         <v>414</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D10" s="12" t="str">
         <f t="shared" ref="D10:D32" si="5">CONCATENATE(A10," ",C10)</f>
         <v>414 合謙學</v>
       </c>
       <c r="E10" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>600</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>601</v>
+      <c r="G10" s="19">
+        <v>30.5</v>
       </c>
       <c r="I10" s="13">
         <v>96</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M10" s="15">
         <v>32</v>
@@ -5371,7 +5374,7 @@
         <v>1.5</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="R10" s="15">
         <v>35</v>
@@ -5388,61 +5391,61 @@
         <v>38.5</v>
       </c>
       <c r="Z10" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC10" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AD10" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE10" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AF10" s="10">
         <v>2022</v>
       </c>
       <c r="AG10" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AH10" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI10" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="AJ10" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK10" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL10" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="AM10" s="9" t="s">
         <v>603</v>
       </c>
-      <c r="AJ10" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK10" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL10" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="AM10" s="9" t="s">
+      <c r="AN10" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="AO10" s="9" t="s">
         <v>604</v>
       </c>
-      <c r="AN10" s="9" t="s">
-        <v>604</v>
-      </c>
-      <c r="AO10" s="9" t="s">
+      <c r="AP10" s="9" t="s">
         <v>605</v>
       </c>
-      <c r="AP10" s="9" t="s">
+      <c r="AQ10" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="AR10" s="9" t="s">
         <v>606</v>
       </c>
-      <c r="AQ10" s="9" t="s">
-        <v>606</v>
-      </c>
-      <c r="AR10" s="9" t="s">
+      <c r="AS10" s="9" t="s">
         <v>607</v>
       </c>
-      <c r="AS10" s="9" t="s">
+      <c r="AT10" s="9" t="s">
         <v>608</v>
-      </c>
-      <c r="AT10" s="9" t="s">
-        <v>609</v>
       </c>
       <c r="AU10" s="18">
         <v>0.32500000000000001</v>
@@ -5451,7 +5454,7 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="AW10" s="9" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AX10" s="9">
         <v>106</v>
@@ -5466,40 +5469,40 @@
         <v>0.45660000000000001</v>
       </c>
       <c r="BB10" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="BC10" s="9">
         <v>14</v>
       </c>
       <c r="BD10" s="18" t="s">
+        <v>610</v>
+      </c>
+      <c r="BE10" s="9" t="s">
         <v>611</v>
       </c>
-      <c r="BE10" s="9" t="s">
+      <c r="BF10" s="11" t="s">
         <v>612</v>
-      </c>
-      <c r="BF10" s="11" t="s">
-        <v>613</v>
       </c>
       <c r="BG10" s="19">
         <v>0.91</v>
       </c>
       <c r="BH10" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI10" s="9" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="BJ10" s="9">
         <v>1030.74</v>
       </c>
       <c r="BK10" s="9" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="BL10" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="BR10" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:70">
@@ -5507,23 +5510,23 @@
         <v>413</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D11" s="12" t="str">
         <f t="shared" si="5"/>
         <v>413 頤昌璞岳</v>
       </c>
       <c r="E11" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="F11" s="13" t="s">
-        <v>583</v>
-      </c>
       <c r="G11" s="14">
-        <v>27.11</v>
+        <v>27.3</v>
       </c>
       <c r="H11" s="13">
         <v>26.83</v>
@@ -5538,7 +5541,7 @@
         <v>24.79</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M11" s="15">
         <v>32</v>
@@ -5555,7 +5558,7 @@
         <v>0.5</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="R11" s="15">
         <v>32</v>
@@ -5572,61 +5575,61 @@
         <v>32.5</v>
       </c>
       <c r="Z11" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AC11" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AD11" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="AE11" s="9" t="s">
         <v>585</v>
-      </c>
-      <c r="AE11" s="9" t="s">
-        <v>586</v>
       </c>
       <c r="AF11" s="10">
         <v>2022</v>
       </c>
       <c r="AG11" s="9" t="s">
+        <v>586</v>
+      </c>
+      <c r="AH11" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI11" s="9" t="s">
         <v>587</v>
       </c>
-      <c r="AH11" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI11" s="9" t="s">
+      <c r="AJ11" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK11" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL11" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="AM11" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="AJ11" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK11" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL11" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="AM11" s="9" t="s">
+      <c r="AN11" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="AN11" s="9" t="s">
+      <c r="AO11" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="AP11" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="AQ11" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="AR11" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="AO11" s="9" t="s">
-        <v>495</v>
-      </c>
-      <c r="AP11" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="AQ11" s="9" t="s">
-        <v>496</v>
-      </c>
-      <c r="AR11" s="9" t="s">
+      <c r="AS11" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="AT11" s="9" t="s">
         <v>591</v>
-      </c>
-      <c r="AS11" s="9" t="s">
-        <v>498</v>
-      </c>
-      <c r="AT11" s="9" t="s">
-        <v>592</v>
       </c>
       <c r="AU11" s="18">
         <v>0.32100000000000001</v>
@@ -5635,7 +5638,7 @@
         <v>0.32100000000000001</v>
       </c>
       <c r="AW11" s="9" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AX11" s="9">
         <v>124</v>
@@ -5650,55 +5653,55 @@
         <v>0.51349999999999996</v>
       </c>
       <c r="BB11" s="20" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="BC11" s="20">
         <v>14</v>
       </c>
       <c r="BD11" s="9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="BE11" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BF11" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BG11" s="19">
         <v>1.01</v>
       </c>
       <c r="BH11" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI11" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="BJ11" s="9">
         <v>595.29</v>
       </c>
       <c r="BK11" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL11" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="BM11" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN11" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO11" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="BP11" s="9" t="s">
         <v>597</v>
       </c>
-      <c r="BP11" s="9" t="s">
-        <v>598</v>
-      </c>
       <c r="BQ11" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR11" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:70">
@@ -5706,26 +5709,26 @@
         <v>101</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>70</v>
       </c>
       <c r="D12" s="12" t="str">
         <f t="shared" si="5"/>
         <v>101 和發大境</v>
       </c>
       <c r="E12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="G12" s="14">
+        <v>29.1</v>
+      </c>
+      <c r="H12" s="13" t="s">
         <v>72</v>
-      </c>
-      <c r="G12" s="14">
-        <v>27.72</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>73</v>
       </c>
       <c r="I12" s="13">
         <v>226</v>
@@ -5737,7 +5740,7 @@
         <v>24.3</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M12" s="15">
         <v>28</v>
@@ -5754,7 +5757,7 @@
         <v>0.5</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R12" s="15">
         <v>34</v>
@@ -5771,7 +5774,7 @@
         <v>35</v>
       </c>
       <c r="Z12" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA12" s="16">
         <v>170</v>
@@ -5783,55 +5786,55 @@
         <v>0.8</v>
       </c>
       <c r="AD12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE12" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="AE12" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="AF12" s="10">
         <v>2022</v>
       </c>
       <c r="AG12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH12" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="AH12" s="9" t="s">
+      <c r="AI12" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="AI12" s="9" t="s">
+      <c r="AJ12" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="AJ12" s="9" t="s">
+      <c r="AK12" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="AK12" s="9" t="s">
+      <c r="AL12" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AL12" s="9" t="s">
+      <c r="AM12" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="AM12" s="9" t="s">
+      <c r="AN12" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="AN12" s="9" t="s">
+      <c r="AO12" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="AO12" s="9" t="s">
+      <c r="AP12" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="AP12" s="9" t="s">
+      <c r="AQ12" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="AQ12" s="9" t="s">
+      <c r="AR12" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="AR12" s="9" t="s">
+      <c r="AS12" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="AS12" s="9" t="s">
+      <c r="AT12" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="AT12" s="9" t="s">
-        <v>92</v>
       </c>
       <c r="AU12" s="17">
         <v>0.33</v>
@@ -5840,7 +5843,7 @@
         <v>0.33</v>
       </c>
       <c r="AW12" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AX12" s="9">
         <v>280</v>
@@ -5855,55 +5858,55 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="BB12" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BC12" s="9">
         <v>15</v>
       </c>
       <c r="BD12" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="BE12" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="BE12" s="9" t="s">
+      <c r="BF12" s="11" t="s">
         <v>96</v>
-      </c>
-      <c r="BF12" s="11" t="s">
-        <v>97</v>
       </c>
       <c r="BG12" s="19">
         <v>1.0900000000000001</v>
       </c>
       <c r="BH12" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="BI12" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="BI12" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="BJ12" s="9">
         <v>1586.57</v>
       </c>
       <c r="BK12" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="BL12" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="BL12" s="9" t="s">
+      <c r="BM12" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="BM12" s="9" t="s">
+      <c r="BN12" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BO12" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="BN12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BO12" s="9" t="s">
+      <c r="BP12" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="BP12" s="9" t="s">
+      <c r="BQ12" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BR12" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="BQ12" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BR12" s="9" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:70">
@@ -5911,26 +5914,30 @@
         <v>306</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D13" s="12" t="str">
         <f t="shared" si="5"/>
         <v>306 華悅城</v>
       </c>
       <c r="E13" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="F13" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="G13" s="21"/>
+      <c r="G13" s="21">
+        <v>25.63</v>
+      </c>
       <c r="H13" s="22">
         <v>25.61</v>
       </c>
-      <c r="I13" s="22"/>
+      <c r="I13" s="22">
+        <v>769</v>
+      </c>
       <c r="J13" s="21">
         <v>29.69</v>
       </c>
@@ -5938,7 +5945,7 @@
         <v>22.7</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="M13" s="15">
         <v>26</v>
@@ -5955,7 +5962,7 @@
         <v>2</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="R13" s="15">
         <v>26</v>
@@ -5972,7 +5979,7 @@
         <v>28</v>
       </c>
       <c r="Z13" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AA13" s="16">
         <v>150</v>
@@ -5981,58 +5988,58 @@
         <v>195</v>
       </c>
       <c r="AC13" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD13" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE13" s="9" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AF13" s="10">
         <v>2022</v>
       </c>
       <c r="AG13" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH13" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="AH13" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="AI13" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="AJ13" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK13" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL13" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM13" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="AJ13" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL13" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM13" s="9" t="s">
+      <c r="AN13" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="AO13" s="9" t="s">
         <v>350</v>
       </c>
-      <c r="AN13" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="AO13" s="9" t="s">
+      <c r="AP13" s="9" t="s">
         <v>351</v>
       </c>
-      <c r="AP13" s="9" t="s">
+      <c r="AQ13" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="AR13" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="AQ13" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="AR13" s="9" t="s">
+      <c r="AS13" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="AS13" s="9" t="s">
+      <c r="AT13" s="9" t="s">
         <v>354</v>
-      </c>
-      <c r="AT13" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="AU13" s="17">
         <v>0.34</v>
@@ -6041,7 +6048,7 @@
         <v>0.34</v>
       </c>
       <c r="AW13" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AX13" s="9">
         <v>776</v>
@@ -6056,55 +6063,55 @@
         <v>0.44359999999999999</v>
       </c>
       <c r="BB13" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="BC13" s="9">
         <v>18</v>
       </c>
       <c r="BD13" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="BE13" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF13" s="11" t="s">
         <v>358</v>
-      </c>
-      <c r="BE13" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BF13" s="11" t="s">
-        <v>359</v>
       </c>
       <c r="BG13" s="19">
         <v>0.9</v>
       </c>
       <c r="BH13" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI13" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="BJ13" s="9">
         <v>2751.33</v>
       </c>
       <c r="BK13" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL13" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BM13" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN13" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO13" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="BP13" s="9" t="s">
         <v>361</v>
       </c>
-      <c r="BP13" s="9" t="s">
-        <v>362</v>
-      </c>
       <c r="BQ13" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR13" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:70">
@@ -6112,26 +6119,26 @@
         <v>405</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D14" s="12" t="str">
         <f t="shared" si="5"/>
         <v>405 新A7</v>
       </c>
       <c r="E14" s="12" t="s">
+        <v>451</v>
+      </c>
+      <c r="F14" s="20" t="s">
         <v>452</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="G14" s="21">
+        <v>27.5</v>
+      </c>
+      <c r="H14" s="22" t="s">
         <v>453</v>
-      </c>
-      <c r="G14" s="21">
-        <v>26.59</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>454</v>
       </c>
       <c r="I14" s="22">
         <v>356</v>
@@ -6143,7 +6150,7 @@
         <v>24.01</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M14" s="15">
         <v>31</v>
@@ -6160,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="R14" s="15">
         <v>32</v>
@@ -6177,7 +6184,7 @@
         <v>33.5</v>
       </c>
       <c r="Z14" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="AA14" s="16">
         <v>180</v>
@@ -6186,58 +6193,58 @@
         <v>200</v>
       </c>
       <c r="AC14" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD14" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE14" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AF14" s="10">
         <v>2022</v>
       </c>
       <c r="AG14" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH14" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="AH14" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="AI14" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="AJ14" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK14" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL14" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM14" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="AJ14" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL14" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM14" s="9" t="s">
+      <c r="AN14" s="9" t="s">
         <v>460</v>
       </c>
-      <c r="AN14" s="9" t="s">
+      <c r="AO14" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="AO14" s="9" t="s">
+      <c r="AP14" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="AP14" s="9" t="s">
+      <c r="AQ14" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR14" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS14" s="9" t="s">
         <v>463</v>
       </c>
-      <c r="AQ14" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR14" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS14" s="9" t="s">
+      <c r="AT14" s="9" t="s">
         <v>464</v>
-      </c>
-      <c r="AT14" s="9" t="s">
-        <v>465</v>
       </c>
       <c r="AU14" s="17">
         <v>0.32</v>
@@ -6246,7 +6253,7 @@
         <v>0.32</v>
       </c>
       <c r="AW14" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AX14" s="9">
         <v>371</v>
@@ -6261,55 +6268,55 @@
         <v>0.46450000000000002</v>
       </c>
       <c r="BB14" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BC14" s="9">
         <v>15</v>
       </c>
       <c r="BD14" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="BE14" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="BF14" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BG14" s="19">
         <v>1</v>
       </c>
       <c r="BH14" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI14" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="BJ14" s="9">
         <v>1538.68</v>
       </c>
       <c r="BK14" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL14" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BM14" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN14" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO14" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="BP14" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="BP14" s="9" t="s">
-        <v>470</v>
-      </c>
       <c r="BQ14" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR14" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:70">
@@ -6317,23 +6324,23 @@
         <v>505</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D15" s="12" t="str">
         <f t="shared" si="5"/>
         <v>505 櫻花澍</v>
       </c>
       <c r="E15" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="F15" s="20" t="s">
         <v>696</v>
       </c>
-      <c r="F15" s="20" t="s">
-        <v>697</v>
-      </c>
       <c r="G15" s="21">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="H15" s="22">
         <v>26.09</v>
@@ -6348,7 +6355,7 @@
         <v>24.04</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="M15" s="15">
         <v>28</v>
@@ -6365,7 +6372,7 @@
         <v>2</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="R15" s="15">
         <v>28</v>
@@ -6382,16 +6389,16 @@
         <v>30</v>
       </c>
       <c r="V15" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W15" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="X15" s="20" t="s">
         <v>699</v>
       </c>
-      <c r="X15" s="20" t="s">
+      <c r="Z15" s="9" t="s">
         <v>700</v>
-      </c>
-      <c r="Z15" s="9" t="s">
-        <v>701</v>
       </c>
       <c r="AA15" s="16">
         <v>165</v>
@@ -6400,58 +6407,58 @@
         <v>195</v>
       </c>
       <c r="AC15" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD15" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AE15" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AF15" s="10">
         <v>2022</v>
       </c>
       <c r="AG15" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AH15" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="AH15" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="AI15" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="AJ15" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK15" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL15" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM15" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="AJ15" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK15" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL15" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM15" s="9" t="s">
+      <c r="AN15" s="9" t="s">
         <v>703</v>
       </c>
-      <c r="AN15" s="9" t="s">
+      <c r="AO15" s="9" t="s">
         <v>704</v>
       </c>
-      <c r="AO15" s="9" t="s">
+      <c r="AP15" s="9" t="s">
         <v>705</v>
       </c>
-      <c r="AP15" s="9" t="s">
+      <c r="AQ15" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="AR15" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS15" s="9" t="s">
         <v>706</v>
       </c>
-      <c r="AQ15" s="9" t="s">
-        <v>706</v>
-      </c>
-      <c r="AR15" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS15" s="9" t="s">
+      <c r="AT15" s="9" t="s">
         <v>707</v>
-      </c>
-      <c r="AT15" s="9" t="s">
-        <v>708</v>
       </c>
       <c r="AU15" s="17">
         <v>0.32</v>
@@ -6460,7 +6467,7 @@
         <v>0.32</v>
       </c>
       <c r="AW15" s="9" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AX15" s="9">
         <v>106</v>
@@ -6475,52 +6482,52 @@
         <v>0.38140000000000002</v>
       </c>
       <c r="BB15" s="9" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="BC15" s="9">
         <v>14</v>
       </c>
       <c r="BD15" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="BE15" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="BE15" s="9" t="s">
-        <v>711</v>
-      </c>
       <c r="BF15" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BG15" s="19">
         <v>1</v>
       </c>
       <c r="BH15" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI15" s="9" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="BJ15" s="9">
         <v>602.07000000000005</v>
       </c>
       <c r="BK15" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL15" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="BN15" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO15" s="9" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="BP15" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="BQ15" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR15" s="9" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="16" spans="1:70" ht="16">
@@ -6528,22 +6535,24 @@
         <v>206</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D16" s="12" t="str">
         <f t="shared" si="5"/>
         <v>206 玄泰V1</v>
       </c>
       <c r="E16" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="F16" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="G16" s="14"/>
+      <c r="G16" s="14">
+        <v>21.3</v>
+      </c>
       <c r="H16" s="13">
         <v>22.46</v>
       </c>
@@ -6557,7 +6566,7 @@
         <v>19.04</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M16" s="15">
         <v>27</v>
@@ -6574,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R16" s="15">
         <v>27</v>
@@ -6591,10 +6600,10 @@
         <v>28</v>
       </c>
       <c r="V16" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z16" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AA16" s="16">
         <v>155</v>
@@ -6603,67 +6612,67 @@
         <v>195</v>
       </c>
       <c r="AC16" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD16" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE16" s="9" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AF16" s="10">
         <v>2023</v>
       </c>
       <c r="AG16" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="AH16" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI16" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="AH16" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI16" s="9" t="s">
+      <c r="AJ16" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK16" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL16" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM16" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="AJ16" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL16" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM16" s="9" t="s">
+      <c r="AN16" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="AN16" s="9" t="s">
+      <c r="AO16" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="AO16" s="9" t="s">
+      <c r="AP16" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="AP16" s="9" t="s">
+      <c r="AQ16" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="AQ16" s="9" t="s">
+      <c r="AR16" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="AR16" s="9" t="s">
+      <c r="AS16" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="AS16" s="9" t="s">
+      <c r="AT16" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="AT16" s="9" t="s">
+      <c r="AU16" s="9" t="s">
         <v>264</v>
-      </c>
-      <c r="AU16" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="AV16" s="18">
         <v>0.31900000000000001</v>
       </c>
       <c r="AW16" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AX16" s="9">
         <v>138</v>
@@ -6672,61 +6681,61 @@
         <v>8</v>
       </c>
       <c r="AZ16" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BA16" s="18">
         <v>0.60160000000000002</v>
       </c>
       <c r="BB16" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="BC16" s="9">
         <v>24</v>
       </c>
       <c r="BD16" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="BE16" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF16" s="11" t="s">
         <v>269</v>
-      </c>
-      <c r="BE16" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BF16" s="11" t="s">
-        <v>270</v>
       </c>
       <c r="BG16" s="19">
         <v>1.05</v>
       </c>
       <c r="BH16" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI16" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="BJ16" s="9">
         <v>911.52</v>
       </c>
       <c r="BK16" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL16" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="BM16" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BN16" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BO16" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="BM16" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BN16" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BO16" s="9" t="s">
+      <c r="BP16" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="BP16" s="9" t="s">
-        <v>274</v>
-      </c>
       <c r="BQ16" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR16" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:70">
@@ -6734,28 +6743,30 @@
         <v>404</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D17" s="12" t="str">
         <f t="shared" si="5"/>
         <v>404 詠勝市中欣</v>
       </c>
       <c r="E17" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="F17" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="F17" s="13" t="s">
-        <v>431</v>
-      </c>
       <c r="G17" s="14">
-        <v>21.19</v>
+        <v>21.3</v>
       </c>
       <c r="H17" s="13">
         <v>32.74</v>
       </c>
-      <c r="I17" s="13"/>
+      <c r="I17" s="13">
+        <v>310</v>
+      </c>
       <c r="J17" s="14">
         <v>48.58</v>
       </c>
@@ -6763,7 +6774,7 @@
         <v>19.559999999999999</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="M17" s="15">
         <v>27</v>
@@ -6780,7 +6791,7 @@
         <v>2.5</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="R17" s="15">
         <v>24</v>
@@ -6797,10 +6808,10 @@
         <v>24.5</v>
       </c>
       <c r="V17" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z17" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AA17" s="16">
         <v>155</v>
@@ -6809,67 +6820,67 @@
         <v>205</v>
       </c>
       <c r="AC17" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD17" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE17" s="25" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AF17" s="10">
         <v>2023</v>
       </c>
       <c r="AG17" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="AH17" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI17" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="AJ17" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="AK17" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL17" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM17" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="AJ17" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="AK17" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL17" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM17" s="9" t="s">
+      <c r="AN17" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="AN17" s="9" t="s">
+      <c r="AO17" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="AO17" s="9" t="s">
+      <c r="AP17" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="AP17" s="9" t="s">
+      <c r="AQ17" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="AR17" s="9" t="s">
         <v>440</v>
       </c>
-      <c r="AQ17" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="AR17" s="9" t="s">
+      <c r="AS17" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="AS17" s="9" t="s">
+      <c r="AT17" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="AT17" s="9" t="s">
+      <c r="AU17" s="9" t="s">
         <v>443</v>
-      </c>
-      <c r="AU17" s="9" t="s">
-        <v>444</v>
       </c>
       <c r="AV17" s="18">
         <v>0.33</v>
       </c>
       <c r="AW17" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AX17" s="9">
         <v>257</v>
@@ -6878,61 +6889,61 @@
         <v>7</v>
       </c>
       <c r="AZ17" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="BA17" s="18">
         <v>0.53259999999999996</v>
       </c>
       <c r="BB17" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="BC17" s="9">
         <v>22</v>
       </c>
       <c r="BD17" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="BE17" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="BF17" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BG17" s="19">
         <v>1.01</v>
       </c>
       <c r="BH17" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI17" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="BJ17" s="9">
         <v>926.66</v>
       </c>
       <c r="BK17" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL17" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BM17" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN17" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO17" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="BP17" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="BQ17" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR17" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:70" ht="16">
@@ -6940,22 +6951,24 @@
         <v>502</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D18" s="12" t="str">
         <f t="shared" si="5"/>
         <v>502 富宇天匯</v>
       </c>
       <c r="E18" s="12" t="s">
+        <v>674</v>
+      </c>
+      <c r="F18" s="20" t="s">
         <v>675</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>676</v>
-      </c>
-      <c r="G18" s="21"/>
+      <c r="G18" s="21">
+        <v>35</v>
+      </c>
       <c r="H18" s="22"/>
       <c r="I18" s="22">
         <v>192</v>
@@ -6963,7 +6976,7 @@
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
       <c r="L18" s="9" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="M18" s="15">
         <v>39</v>
@@ -6980,7 +6993,7 @@
         <v>2</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="R18" s="15">
         <v>45</v>
@@ -6997,7 +7010,7 @@
         <v>47.5</v>
       </c>
       <c r="Z18" s="9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AA18" s="16">
         <v>160</v>
@@ -7006,58 +7019,58 @@
         <v>205</v>
       </c>
       <c r="AC18" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD18" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE18" s="9" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AF18" s="10">
         <v>2023</v>
       </c>
       <c r="AG18" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="AH18" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI18" s="9" t="s">
         <v>681</v>
       </c>
-      <c r="AH18" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI18" s="9" t="s">
+      <c r="AJ18" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK18" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL18" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM18" s="9" t="s">
         <v>682</v>
       </c>
-      <c r="AJ18" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK18" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL18" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM18" s="9" t="s">
+      <c r="AN18" s="9" t="s">
         <v>683</v>
       </c>
-      <c r="AN18" s="9" t="s">
+      <c r="AO18" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="AO18" s="9" t="s">
+      <c r="AP18" s="9" t="s">
         <v>685</v>
       </c>
-      <c r="AP18" s="9" t="s">
+      <c r="AQ18" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR18" s="9" t="s">
         <v>686</v>
       </c>
-      <c r="AQ18" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="AR18" s="9" t="s">
+      <c r="AS18" s="9" t="s">
         <v>687</v>
       </c>
-      <c r="AS18" s="9" t="s">
-        <v>688</v>
-      </c>
       <c r="AT18" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AU18" s="18">
         <v>0.33500000000000002</v>
@@ -7066,7 +7079,7 @@
         <v>0.33500000000000002</v>
       </c>
       <c r="AW18" s="9" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AX18" s="9">
         <v>266</v>
@@ -7081,55 +7094,55 @@
         <v>0.49540000000000001</v>
       </c>
       <c r="BB18" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BC18" s="9">
         <v>15</v>
       </c>
       <c r="BD18" s="18" t="s">
+        <v>689</v>
+      </c>
+      <c r="BE18" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="BF18" s="11" t="s">
         <v>690</v>
-      </c>
-      <c r="BE18" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="BF18" s="11" t="s">
-        <v>691</v>
       </c>
       <c r="BG18" s="19">
         <v>1.03</v>
       </c>
       <c r="BH18" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI18" s="9" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="BJ18" s="9">
         <v>1471.38</v>
       </c>
       <c r="BK18" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL18" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="BM18" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN18" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO18" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="BP18" s="9" t="s">
         <v>693</v>
       </c>
-      <c r="BP18" s="9" t="s">
-        <v>694</v>
-      </c>
       <c r="BQ18" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR18" s="9" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="19" spans="1:70">
@@ -7137,27 +7150,29 @@
         <v>302</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D19" s="12" t="str">
         <f t="shared" si="5"/>
         <v>302 欣時代</v>
       </c>
       <c r="E19" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="G19" s="14">
+        <v>24.02</v>
+      </c>
+      <c r="H19" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="G19" s="14"/>
-      <c r="H19" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>752</v>
+      <c r="I19" s="13">
+        <v>154</v>
       </c>
       <c r="J19" s="14">
         <v>28.96</v>
@@ -7166,7 +7181,7 @@
         <v>19.2</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="M19" s="15">
         <v>27</v>
@@ -7183,7 +7198,7 @@
         <v>1</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R19" s="15">
         <v>27</v>
@@ -7200,10 +7215,10 @@
         <v>28</v>
       </c>
       <c r="V19" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z19" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AA19" s="16">
         <v>170</v>
@@ -7212,67 +7227,67 @@
         <v>205</v>
       </c>
       <c r="AC19" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD19" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE19" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AF19" s="10">
         <v>2023</v>
       </c>
       <c r="AG19" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="AH19" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI19" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="AH19" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI19" s="9" t="s">
+      <c r="AJ19" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK19" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL19" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM19" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="AJ19" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK19" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL19" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM19" s="9" t="s">
+      <c r="AN19" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="AN19" s="9" t="s">
+      <c r="AO19" s="9" t="s">
         <v>328</v>
       </c>
-      <c r="AO19" s="9" t="s">
+      <c r="AP19" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="AP19" s="12" t="s">
+      <c r="AQ19" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="AR19" s="9" t="s">
         <v>330</v>
       </c>
-      <c r="AQ19" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="AR19" s="9" t="s">
+      <c r="AS19" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="AS19" s="9" t="s">
+      <c r="AT19" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="AT19" s="9" t="s">
-        <v>333</v>
-      </c>
       <c r="AU19" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AV19" s="18">
         <v>0.33500000000000002</v>
       </c>
       <c r="AW19" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AX19" s="9">
         <v>235</v>
@@ -7281,61 +7296,61 @@
         <v>4</v>
       </c>
       <c r="AZ19" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="BA19" s="18">
         <v>0.57489999999999997</v>
       </c>
       <c r="BB19" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BC19" s="9">
         <v>30</v>
       </c>
       <c r="BD19" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="BE19" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF19" s="11" t="s">
         <v>337</v>
-      </c>
-      <c r="BE19" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BF19" s="11" t="s">
-        <v>338</v>
       </c>
       <c r="BG19" s="19">
         <v>0.91</v>
       </c>
       <c r="BH19" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI19" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="BJ19" s="9">
         <v>713.17</v>
       </c>
       <c r="BK19" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL19" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BM19" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN19" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO19" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="BP19" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="BP19" s="9" t="s">
-        <v>341</v>
-      </c>
       <c r="BQ19" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR19" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:70">
@@ -7343,26 +7358,26 @@
         <v>313</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D20" s="12" t="str">
         <f t="shared" si="5"/>
         <v>313 大亮時代A7</v>
       </c>
       <c r="E20" s="12" t="s">
+        <v>616</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>617</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="G20" s="14">
+        <v>31</v>
+      </c>
+      <c r="H20" s="13" t="s">
         <v>618</v>
-      </c>
-      <c r="G20" s="14">
-        <v>29.4</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>619</v>
       </c>
       <c r="I20" s="13">
         <v>167</v>
@@ -7374,7 +7389,7 @@
         <v>27.17</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="M20" s="15">
         <v>35</v>
@@ -7391,7 +7406,7 @@
         <v>0.5</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="R20" s="15">
         <v>35</v>
@@ -7408,7 +7423,7 @@
         <v>35.5</v>
       </c>
       <c r="Z20" s="9" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AA20" s="16">
         <v>148</v>
@@ -7417,58 +7432,58 @@
         <v>169</v>
       </c>
       <c r="AC20" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD20" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE20" s="9" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AF20" s="10">
         <v>2023</v>
       </c>
       <c r="AG20" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AH20" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI20" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="AJ20" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK20" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL20" s="9" t="s">
         <v>623</v>
       </c>
-      <c r="AJ20" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK20" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL20" s="9" t="s">
+      <c r="AM20" s="9" t="s">
         <v>624</v>
       </c>
-      <c r="AM20" s="9" t="s">
+      <c r="AN20" s="9" t="s">
         <v>625</v>
       </c>
-      <c r="AN20" s="9" t="s">
+      <c r="AO20" s="9" t="s">
         <v>626</v>
       </c>
-      <c r="AO20" s="9" t="s">
+      <c r="AP20" s="9" t="s">
         <v>627</v>
       </c>
-      <c r="AP20" s="9" t="s">
+      <c r="AQ20" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="AR20" s="9" t="s">
         <v>628</v>
       </c>
-      <c r="AQ20" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="AR20" s="9" t="s">
+      <c r="AS20" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="AT20" s="9" t="s">
         <v>629</v>
-      </c>
-      <c r="AS20" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="AT20" s="9" t="s">
-        <v>630</v>
       </c>
       <c r="AU20" s="18">
         <v>0.33900000000000002</v>
@@ -7477,7 +7492,7 @@
         <v>0.33900000000000002</v>
       </c>
       <c r="AW20" s="9" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AX20" s="9">
         <v>87</v>
@@ -7492,49 +7507,49 @@
         <v>0.50270000000000004</v>
       </c>
       <c r="BB20" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BC20" s="9">
         <v>15</v>
       </c>
       <c r="BD20" s="18" t="s">
+        <v>631</v>
+      </c>
+      <c r="BE20" s="9" t="s">
         <v>632</v>
       </c>
-      <c r="BE20" s="9" t="s">
+      <c r="BF20" s="11" t="s">
         <v>633</v>
-      </c>
-      <c r="BF20" s="11" t="s">
-        <v>634</v>
       </c>
       <c r="BG20" s="19">
         <v>0.36</v>
       </c>
       <c r="BH20" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI20" s="9" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="BJ20" s="9">
         <v>332.5</v>
       </c>
       <c r="BK20" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="BL20" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="BO20" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="BP20" s="9" t="s">
         <v>636</v>
       </c>
-      <c r="BP20" s="9" t="s">
-        <v>637</v>
-      </c>
       <c r="BQ20" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR20" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" spans="1:70">
@@ -7542,26 +7557,26 @@
         <v>407</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D21" s="12" t="str">
         <f t="shared" si="5"/>
         <v>407 富宇哈佛苑</v>
       </c>
       <c r="E21" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="F21" s="13" t="s">
         <v>474</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="G21" s="14">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="H21" s="13" t="s">
         <v>475</v>
-      </c>
-      <c r="G21" s="14">
-        <v>34.08</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>476</v>
       </c>
       <c r="I21" s="13">
         <v>447</v>
@@ -7573,7 +7588,7 @@
         <v>22.76</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M21" s="15">
         <v>33</v>
@@ -7590,7 +7605,7 @@
         <v>2.5</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R21" s="15">
         <v>44</v>
@@ -7607,7 +7622,7 @@
         <v>46.5</v>
       </c>
       <c r="Z21" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AA21" s="16">
         <v>180</v>
@@ -7616,67 +7631,67 @@
         <v>205</v>
       </c>
       <c r="AC21" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD21" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE21" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AF21" s="10">
         <v>2023</v>
       </c>
       <c r="AG21" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AH21" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI21" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="AJ21" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK21" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL21" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM21" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="AJ21" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK21" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL21" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM21" s="9" t="s">
+      <c r="AN21" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="AN21" s="9" t="s">
-        <v>482</v>
-      </c>
       <c r="AO21" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="AP21" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="AP21" s="9" t="s">
+      <c r="AQ21" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR21" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="AQ21" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="AR21" s="9" t="s">
+      <c r="AS21" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="AS21" s="9" t="s">
-        <v>204</v>
-      </c>
       <c r="AT21" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AU21" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AV21" s="18">
         <v>0.33500000000000002</v>
       </c>
       <c r="AW21" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AX21" s="9">
         <v>483</v>
@@ -7685,61 +7700,61 @@
         <v>8</v>
       </c>
       <c r="AZ21" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="BA21" s="18">
         <v>0.44180000000000003</v>
       </c>
       <c r="BB21" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BC21" s="9">
         <v>24</v>
       </c>
       <c r="BD21" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="BE21" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="BF21" s="11" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BG21" s="19">
         <v>1.01</v>
       </c>
       <c r="BH21" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI21" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="BJ21" s="9">
         <v>2155.85</v>
       </c>
       <c r="BK21" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL21" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BM21" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN21" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO21" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="BP21" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="BQ21" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR21" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:70" ht="16">
@@ -7747,29 +7762,29 @@
         <v>410</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D22" s="12" t="str">
         <f t="shared" si="5"/>
         <v>410 新未來3</v>
       </c>
       <c r="E22" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="F22" s="20" t="s">
         <v>526</v>
       </c>
-      <c r="F22" s="20" t="s">
-        <v>527</v>
-      </c>
       <c r="G22" s="21">
-        <v>30.02</v>
+        <v>30.1</v>
       </c>
       <c r="H22" s="22">
         <v>29.48</v>
       </c>
       <c r="I22" s="22">
-        <v>66</v>
+        <v>599</v>
       </c>
       <c r="J22" s="21">
         <v>32</v>
@@ -7778,7 +7793,7 @@
         <v>25.65</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M22" s="15">
         <v>33</v>
@@ -7795,7 +7810,7 @@
         <v>2.5</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="R22" s="15">
         <v>33</v>
@@ -7812,7 +7827,7 @@
         <v>35.5</v>
       </c>
       <c r="Z22" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AA22" s="16">
         <v>190</v>
@@ -7821,58 +7836,58 @@
         <v>190</v>
       </c>
       <c r="AC22" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD22" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE22" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AF22" s="10">
         <v>2023</v>
       </c>
       <c r="AG22" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AH22" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI22" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="AJ22" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK22" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL22" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM22" s="9" t="s">
         <v>531</v>
       </c>
-      <c r="AJ22" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK22" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL22" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM22" s="9" t="s">
-        <v>532</v>
-      </c>
       <c r="AN22" s="9" t="s">
+        <v>514</v>
+      </c>
+      <c r="AO22" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="AO22" s="9" t="s">
+      <c r="AP22" s="9" t="s">
         <v>516</v>
       </c>
-      <c r="AP22" s="9" t="s">
+      <c r="AQ22" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="AR22" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="AQ22" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="AR22" s="9" t="s">
+      <c r="AS22" s="9" t="s">
         <v>518</v>
       </c>
-      <c r="AS22" s="9" t="s">
-        <v>519</v>
-      </c>
       <c r="AT22" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AU22" s="18">
         <v>0.3327</v>
@@ -7881,7 +7896,7 @@
         <v>0.3327</v>
       </c>
       <c r="AW22" s="9" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AX22" s="9">
         <v>582</v>
@@ -7896,55 +7911,55 @@
         <v>0.38300000000000001</v>
       </c>
       <c r="BB22" s="9" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="BC22" s="9">
         <v>22</v>
       </c>
       <c r="BD22" s="18" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="BE22" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BF22" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BG22" s="19">
         <v>1</v>
       </c>
       <c r="BH22" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI22" s="9" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="BJ22" s="9">
         <v>2513.2199999999998</v>
       </c>
       <c r="BK22" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL22" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BM22" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN22" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO22" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="BP22" s="9" t="s">
         <v>537</v>
       </c>
-      <c r="BP22" s="9" t="s">
-        <v>538</v>
-      </c>
       <c r="BQ22" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR22" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:70">
@@ -7952,26 +7967,26 @@
         <v>311</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D23" s="12" t="str">
         <f t="shared" si="5"/>
         <v>311 文華天際</v>
       </c>
       <c r="E23" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="F23" s="20" t="s">
         <v>389</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="G23" s="21">
+        <v>26.3</v>
+      </c>
+      <c r="H23" s="22" t="s">
         <v>390</v>
-      </c>
-      <c r="G23" s="21">
-        <v>25.71</v>
-      </c>
-      <c r="H23" s="22" t="s">
-        <v>391</v>
       </c>
       <c r="I23" s="22">
         <v>745</v>
@@ -7983,7 +7998,7 @@
         <v>23.19</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="M23" s="15">
         <v>27</v>
@@ -8000,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="R23" s="15">
         <v>32</v>
@@ -8017,7 +8032,7 @@
         <v>33</v>
       </c>
       <c r="Z23" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AA23" s="16">
         <v>115</v>
@@ -8026,58 +8041,58 @@
         <v>217</v>
       </c>
       <c r="AC23" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD23" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="AE23" s="9" t="s">
         <v>395</v>
-      </c>
-      <c r="AE23" s="9" t="s">
-        <v>396</v>
       </c>
       <c r="AF23" s="10">
         <v>2024</v>
       </c>
       <c r="AG23" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="AH23" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI23" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="AH23" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI23" s="9" t="s">
+      <c r="AJ23" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK23" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL23" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM23" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="AJ23" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL23" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM23" s="9" t="s">
+      <c r="AN23" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="AN23" s="9" t="s">
+      <c r="AO23" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="AP23" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="AQ23" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR23" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AS23" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="AO23" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="AP23" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="AQ23" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR23" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS23" s="9" t="s">
+      <c r="AT23" s="9" t="s">
         <v>401</v>
-      </c>
-      <c r="AT23" s="9" t="s">
-        <v>402</v>
       </c>
       <c r="AU23" s="17">
         <v>0.32500000000000001</v>
@@ -8086,7 +8101,7 @@
         <v>0.33</v>
       </c>
       <c r="AW23" s="9" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AX23" s="9">
         <v>478</v>
@@ -8101,52 +8116,52 @@
         <v>0.3347</v>
       </c>
       <c r="BB23" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="BC23" s="9">
         <v>22</v>
       </c>
       <c r="BD23" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="BE23" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="BF23" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BG23" s="19">
         <v>1</v>
       </c>
       <c r="BH23" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI23" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="BJ23" s="9">
         <v>1998.07</v>
       </c>
       <c r="BK23" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL23" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BN23" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO23" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="BP23" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="BQ23" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="BP23" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="BQ23" s="9" t="s">
-        <v>408</v>
-      </c>
       <c r="BR23" s="9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24" spans="1:70">
@@ -8154,26 +8169,29 @@
         <v>417</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D24" s="12" t="str">
         <f t="shared" si="5"/>
         <v>417 頤昌澄岳</v>
       </c>
       <c r="E24" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="F24" s="20" t="s">
         <v>660</v>
       </c>
-      <c r="F24" s="20" t="s">
-        <v>661</v>
+      <c r="G24" s="19">
+        <v>32.9</v>
       </c>
       <c r="H24" s="22">
         <v>25.41</v>
       </c>
       <c r="I24" s="22" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="J24" s="19">
         <v>25.92</v>
@@ -8182,7 +8200,7 @@
         <v>25.06</v>
       </c>
       <c r="Q24" s="15" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="R24" s="15">
         <v>39</v>
@@ -8195,7 +8213,7 @@
         <v>39.5</v>
       </c>
       <c r="Z24" s="9" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AA24" s="16">
         <v>175</v>
@@ -8204,52 +8222,52 @@
         <v>210</v>
       </c>
       <c r="AD24" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE24" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AF24" s="10">
         <v>2024</v>
       </c>
       <c r="AG24" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AH24" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI24" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="AJ24" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK24" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL24" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="AM24" s="9" t="s">
         <v>664</v>
       </c>
-      <c r="AJ24" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK24" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL24" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="AM24" s="9" t="s">
+      <c r="AN24" s="9" t="s">
         <v>665</v>
       </c>
-      <c r="AN24" s="9" t="s">
-        <v>666</v>
-      </c>
       <c r="AO24" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="AP24" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="AP24" s="9" t="s">
-        <v>496</v>
-      </c>
       <c r="AQ24" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AR24" s="9" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AS24" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AU24" s="18">
         <v>0.33</v>
@@ -8258,7 +8276,7 @@
         <v>0.33</v>
       </c>
       <c r="AW24" s="9" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AX24" s="9">
         <v>140</v>
@@ -8273,46 +8291,46 @@
         <v>0.38429999999999997</v>
       </c>
       <c r="BB24" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="BC24" s="9">
         <v>15</v>
       </c>
       <c r="BD24" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="BE24" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="BF24" s="11" t="s">
         <v>668</v>
-      </c>
-      <c r="BE24" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="BF24" s="11" t="s">
-        <v>669</v>
       </c>
       <c r="BG24" s="19">
         <v>0.97</v>
       </c>
       <c r="BH24" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BI24" s="9" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="BJ24" s="19">
         <v>665.31</v>
       </c>
       <c r="BK24" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL24" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BO24" s="9" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="BP24" s="9" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="BR24" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:70">
@@ -8320,26 +8338,26 @@
         <v>416</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D25" s="12" t="str">
         <f t="shared" si="5"/>
         <v>416 維特魯威</v>
       </c>
       <c r="E25" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="F25" s="20" t="s">
         <v>639</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="G25" s="19">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>640</v>
-      </c>
-      <c r="G25" s="19">
-        <v>31.65</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>641</v>
       </c>
       <c r="I25" s="9">
         <v>97</v>
@@ -8351,7 +8369,7 @@
         <v>27.48</v>
       </c>
       <c r="Q25" s="15" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="R25" s="15">
         <v>37.799999999999997</v>
@@ -8364,52 +8382,52 @@
         <v>41.65</v>
       </c>
       <c r="AD25" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE25" s="9" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AF25" s="10">
         <v>2024</v>
       </c>
       <c r="AG25" s="9" t="s">
+        <v>643</v>
+      </c>
+      <c r="AH25" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI25" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="AH25" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI25" s="9" t="s">
+      <c r="AJ25" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK25" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL25" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="AM25" s="9" t="s">
         <v>645</v>
       </c>
-      <c r="AJ25" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK25" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL25" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="AM25" s="9" t="s">
+      <c r="AN25" s="9" t="s">
         <v>646</v>
       </c>
-      <c r="AN25" s="9" t="s">
+      <c r="AO25" s="9" t="s">
         <v>647</v>
       </c>
-      <c r="AO25" s="9" t="s">
+      <c r="AP25" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="AP25" s="9" t="s">
+      <c r="AQ25" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="AR25" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="AQ25" s="9" t="s">
-        <v>649</v>
-      </c>
-      <c r="AR25" s="9" t="s">
+      <c r="AS25" s="9" t="s">
         <v>650</v>
-      </c>
-      <c r="AS25" s="9" t="s">
-        <v>651</v>
       </c>
       <c r="AU25" s="18">
         <v>0.33400000000000002</v>
@@ -8418,7 +8436,7 @@
         <v>0.33400000000000002</v>
       </c>
       <c r="AW25" s="9" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AX25" s="9">
         <v>123</v>
@@ -8433,46 +8451,46 @@
         <v>0.37569999999999998</v>
       </c>
       <c r="BB25" s="9" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="BC25" s="9">
         <v>28</v>
       </c>
       <c r="BD25" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="BE25" s="9" t="s">
         <v>654</v>
       </c>
-      <c r="BE25" s="9" t="s">
+      <c r="BF25" s="11" t="s">
         <v>655</v>
-      </c>
-      <c r="BF25" s="11" t="s">
-        <v>656</v>
       </c>
       <c r="BG25" s="19">
         <v>1.02</v>
       </c>
       <c r="BH25" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BI25" s="9" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="BJ25" s="19">
         <v>586.6</v>
       </c>
       <c r="BK25" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL25" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BO25" s="9" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="BP25" s="9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="BR25" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:70">
@@ -8480,22 +8498,24 @@
         <v>201</v>
       </c>
       <c r="B26" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>189</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>190</v>
       </c>
       <c r="D26" s="12" t="str">
         <f t="shared" si="5"/>
         <v>201 富宇上城</v>
       </c>
       <c r="E26" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="F26" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G26" s="14"/>
+      <c r="G26" s="14">
+        <v>33.5</v>
+      </c>
       <c r="H26" s="13"/>
       <c r="I26" s="13">
         <v>470</v>
@@ -8503,7 +8523,7 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M26" s="15">
         <v>30</v>
@@ -8520,7 +8540,7 @@
         <v>2.5</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="R26" s="15">
         <v>44</v>
@@ -8537,7 +8557,7 @@
         <v>46.5</v>
       </c>
       <c r="Z26" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AA26" s="16">
         <v>170</v>
@@ -8546,67 +8566,67 @@
         <v>205</v>
       </c>
       <c r="AC26" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD26" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE26" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF26" s="10">
         <v>2025</v>
       </c>
       <c r="AG26" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="AH26" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI26" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="AH26" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI26" s="9" t="s">
+      <c r="AJ26" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK26" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL26" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM26" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="AJ26" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK26" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL26" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM26" s="9" t="s">
+      <c r="AN26" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="AN26" s="9" t="s">
+      <c r="AO26" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="AO26" s="9" t="s">
+      <c r="AP26" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="AP26" s="9" t="s">
+      <c r="AQ26" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="AR26" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="AQ26" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="AR26" s="9" t="s">
+      <c r="AS26" s="9" t="s">
         <v>203</v>
       </c>
-      <c r="AS26" s="9" t="s">
+      <c r="AT26" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="AT26" s="9" t="s">
+      <c r="AU26" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="AU26" s="9" t="s">
-        <v>206</v>
       </c>
       <c r="AV26" s="18">
         <v>0.33500000000000002</v>
       </c>
       <c r="AW26" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AX26" s="9">
         <v>832</v>
@@ -8615,61 +8635,61 @@
         <v>0</v>
       </c>
       <c r="AZ26" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BA26" s="18">
         <v>0.31069999999999998</v>
       </c>
       <c r="BB26" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BC26" s="9">
         <v>24</v>
       </c>
       <c r="BD26" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="BE26" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="BE26" s="9" t="s">
+      <c r="BF26" s="11" t="s">
         <v>211</v>
-      </c>
-      <c r="BF26" s="11" t="s">
-        <v>212</v>
       </c>
       <c r="BG26" s="19">
         <v>1.1200000000000001</v>
       </c>
       <c r="BH26" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI26" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BJ26" s="9">
         <v>4046.9</v>
       </c>
       <c r="BK26" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL26" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="BM26" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BN26" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BO26" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="BM26" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BN26" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BO26" s="9" t="s">
+      <c r="BP26" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="BP26" s="9" t="s">
-        <v>216</v>
-      </c>
       <c r="BQ26" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR26" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:70">
@@ -8677,26 +8697,26 @@
         <v>202</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D27" s="12" t="str">
         <f t="shared" si="5"/>
         <v>202 禾悅花園</v>
       </c>
       <c r="E27" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="F27" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="G27" s="14">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="H27" s="13" t="s">
         <v>219</v>
-      </c>
-      <c r="G27" s="14">
-        <v>29.88</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>220</v>
       </c>
       <c r="I27" s="13">
         <v>961</v>
@@ -8708,7 +8728,7 @@
         <v>21.36</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M27" s="15">
         <v>28</v>
@@ -8725,7 +8745,7 @@
         <v>0.5</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R27" s="15">
         <v>35</v>
@@ -8742,7 +8762,7 @@
         <v>36</v>
       </c>
       <c r="Z27" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AA27" s="16">
         <v>130</v>
@@ -8751,67 +8771,67 @@
         <v>200</v>
       </c>
       <c r="AC27" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD27" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE27" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AF27" s="10">
         <v>2025</v>
       </c>
       <c r="AG27" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH27" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI27" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="AJ27" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK27" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL27" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM27" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="AJ27" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK27" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL27" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM27" s="9" t="s">
+      <c r="AN27" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="AN27" s="9" t="s">
+      <c r="AO27" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="AO27" s="9" t="s">
+      <c r="AP27" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="AP27" s="12" t="s">
+      <c r="AQ27" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="AR27" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="AQ27" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="AR27" s="9" t="s">
+      <c r="AS27" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="AS27" s="9" t="s">
+      <c r="AT27" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="AT27" s="9" t="s">
-        <v>232</v>
-      </c>
       <c r="AU27" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AV27" s="18">
         <v>0.33500000000000002</v>
       </c>
       <c r="AW27" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AX27" s="9">
         <v>1044</v>
@@ -8820,61 +8840,61 @@
         <v>0</v>
       </c>
       <c r="AZ27" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BA27" s="18">
         <v>0.52939999999999998</v>
       </c>
       <c r="BB27" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BC27" s="9">
         <v>15</v>
       </c>
       <c r="BD27" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="BE27" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="BE27" s="9" t="s">
+      <c r="BF27" s="11" t="s">
         <v>237</v>
-      </c>
-      <c r="BF27" s="11" t="s">
-        <v>238</v>
       </c>
       <c r="BG27" s="19">
         <v>1.02</v>
       </c>
       <c r="BH27" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI27" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="BJ27" s="9">
         <v>4720.8900000000003</v>
       </c>
       <c r="BK27" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL27" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="BM27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO27" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="BP27" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="BP27" s="9" t="s">
-        <v>241</v>
-      </c>
       <c r="BQ27" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR27" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:70">
@@ -8882,22 +8902,24 @@
         <v>301</v>
       </c>
       <c r="B28" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>297</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>298</v>
       </c>
       <c r="D28" s="12" t="str">
         <f t="shared" si="5"/>
         <v>301 允將大作</v>
       </c>
       <c r="E28" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="F28" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="F28" s="20" t="s">
-        <v>300</v>
-      </c>
-      <c r="G28" s="21"/>
+      <c r="G28" s="21">
+        <v>30.7</v>
+      </c>
       <c r="H28" s="22"/>
       <c r="I28" s="22">
         <v>416</v>
@@ -8905,7 +8927,7 @@
       <c r="J28" s="21"/>
       <c r="K28" s="21"/>
       <c r="L28" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="M28" s="15">
         <v>35</v>
@@ -8922,7 +8944,7 @@
         <v>1.5</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="R28" s="15">
         <v>38</v>
@@ -8939,7 +8961,7 @@
         <v>40.5</v>
       </c>
       <c r="Z28" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AA28" s="16">
         <v>140</v>
@@ -8948,58 +8970,58 @@
         <v>210</v>
       </c>
       <c r="AC28" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD28" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE28" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AF28" s="10">
         <v>2025</v>
       </c>
       <c r="AG28" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH28" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI28" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="AJ28" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK28" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL28" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM28" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="AJ28" s="24" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK28" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL28" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM28" s="9" t="s">
+      <c r="AN28" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="AN28" s="9" t="s">
+      <c r="AO28" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="AO28" s="9" t="s">
+      <c r="AP28" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="AP28" s="9" t="s">
+      <c r="AQ28" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="AR28" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="AQ28" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="AR28" s="9" t="s">
+      <c r="AS28" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="AS28" s="9" t="s">
+      <c r="AT28" s="9" t="s">
         <v>311</v>
-      </c>
-      <c r="AT28" s="9" t="s">
-        <v>312</v>
       </c>
       <c r="AU28" s="18">
         <v>0.33800000000000002</v>
@@ -9008,7 +9030,7 @@
         <v>0.33800000000000002</v>
       </c>
       <c r="AW28" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AX28" s="9">
         <v>530</v>
@@ -9023,55 +9045,55 @@
         <v>0.45529999999999998</v>
       </c>
       <c r="BB28" s="9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="BC28" s="9">
         <v>31</v>
       </c>
       <c r="BD28" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="BE28" s="9" t="s">
         <v>315</v>
       </c>
-      <c r="BE28" s="9" t="s">
-        <v>316</v>
-      </c>
       <c r="BF28" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="BG28" s="19">
         <v>1.01</v>
       </c>
       <c r="BH28" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI28" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="BJ28" s="9">
         <v>1554.48</v>
       </c>
       <c r="BK28" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL28" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="BM28" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BN28" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BO28" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="BM28" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BN28" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BO28" s="9" t="s">
-        <v>319</v>
-      </c>
       <c r="BP28" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BQ28" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BR28" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:70">
@@ -9079,29 +9101,29 @@
         <v>108</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D29" s="12" t="str">
         <f t="shared" si="5"/>
         <v>108 豐邑氧森</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F29" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G29" s="19">
+        <v>36.630000000000003</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="G29" s="19">
-        <v>36.78</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>165</v>
-      </c>
       <c r="I29" s="9">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J29" s="19">
         <v>38.119999999999997</v>
@@ -9110,7 +9132,7 @@
         <v>35.590000000000003</v>
       </c>
       <c r="Q29" s="15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R29" s="15">
         <v>41</v>
@@ -9123,7 +9145,7 @@
         <v>41</v>
       </c>
       <c r="Z29" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA29" s="16">
         <v>200</v>
@@ -9132,52 +9154,52 @@
         <v>200</v>
       </c>
       <c r="AD29" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE29" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AF29" s="10">
         <v>2025</v>
       </c>
       <c r="AG29" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH29" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI29" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="AH29" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI29" s="9" t="s">
+      <c r="AJ29" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="AJ29" s="9" t="s">
+      <c r="AK29" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL29" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="AK29" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL29" s="9" t="s">
+      <c r="AM29" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="AM29" s="9" t="s">
+      <c r="AN29" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="AO29" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="AN29" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="AO29" s="9" t="s">
+      <c r="AP29" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="AP29" s="9" t="s">
+      <c r="AQ29" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="AQ29" s="9" t="s">
+      <c r="AR29" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="AR29" s="9" t="s">
+      <c r="AS29" s="9" t="s">
         <v>177</v>
-      </c>
-      <c r="AS29" s="9" t="s">
-        <v>178</v>
       </c>
       <c r="AU29" s="18">
         <v>0.33110000000000001</v>
@@ -9186,7 +9208,7 @@
         <v>0.33110000000000001</v>
       </c>
       <c r="AW29" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AX29" s="9">
         <v>320</v>
@@ -9201,46 +9223,46 @@
         <v>0.2928</v>
       </c>
       <c r="BB29" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="BC29" s="9">
         <v>21</v>
       </c>
       <c r="BD29" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="BE29" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="BE29" s="9" t="s">
+      <c r="BF29" s="11" t="s">
         <v>182</v>
-      </c>
-      <c r="BF29" s="11" t="s">
-        <v>183</v>
       </c>
       <c r="BG29" s="19">
         <v>1.1399999999999999</v>
       </c>
       <c r="BH29" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="BI29" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="BI29" s="9" t="s">
-        <v>185</v>
       </c>
       <c r="BJ29" s="19">
         <v>1761.89</v>
       </c>
       <c r="BK29" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL29" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="BO29" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="BO29" s="9" t="s">
+      <c r="BP29" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BP29" s="9" t="s">
-        <v>188</v>
-      </c>
       <c r="BR29" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:70">
@@ -9248,22 +9270,24 @@
         <v>403</v>
       </c>
       <c r="B30" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>409</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>410</v>
       </c>
       <c r="D30" s="12" t="str">
         <f t="shared" si="5"/>
         <v>403 捷市達</v>
       </c>
       <c r="E30" s="12" t="s">
+        <v>410</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>411</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>412</v>
-      </c>
-      <c r="G30" s="14"/>
+      <c r="G30" s="14">
+        <v>33.700000000000003</v>
+      </c>
       <c r="H30" s="13"/>
       <c r="I30" s="13">
         <v>628</v>
@@ -9271,7 +9295,7 @@
       <c r="J30" s="14"/>
       <c r="K30" s="14"/>
       <c r="L30" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="M30" s="15">
         <v>35</v>
@@ -9288,7 +9312,7 @@
         <v>1.5</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R30" s="15">
         <v>45</v>
@@ -9305,7 +9329,7 @@
         <v>46.5</v>
       </c>
       <c r="Z30" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AA30" s="16">
         <v>175</v>
@@ -9314,67 +9338,67 @@
         <v>205</v>
       </c>
       <c r="AC30" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AD30" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE30" s="25" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AF30" s="10">
         <v>2025</v>
       </c>
       <c r="AG30" s="25" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AH30" s="9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AI30" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="AJ30" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK30" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL30" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="AM30" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="AJ30" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK30" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL30" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM30" s="9" t="s">
+      <c r="AN30" s="9" t="s">
         <v>418</v>
       </c>
-      <c r="AN30" s="9" t="s">
+      <c r="AO30" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AP30" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="AQ30" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="AR30" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="AS30" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="AO30" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="AP30" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="AQ30" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="AR30" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="AS30" s="9" t="s">
+      <c r="AT30" s="9" t="s">
         <v>420</v>
       </c>
-      <c r="AT30" s="9" t="s">
-        <v>421</v>
-      </c>
       <c r="AU30" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AV30" s="18">
         <v>0.32</v>
       </c>
       <c r="AW30" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AX30" s="9">
         <v>771</v>
@@ -9383,61 +9407,61 @@
         <v>31</v>
       </c>
       <c r="AZ30" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="BA30" s="18">
         <v>0.49530000000000002</v>
       </c>
       <c r="BB30" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="BC30" s="9">
         <v>29</v>
       </c>
       <c r="BD30" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="BE30" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="BF30" s="11" t="s">
         <v>425</v>
-      </c>
-      <c r="BE30" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BF30" s="11" t="s">
-        <v>426</v>
       </c>
       <c r="BG30" s="19">
         <v>0.97</v>
       </c>
       <c r="BH30" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="BI30" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="BJ30" s="9">
         <v>2067.2399999999998</v>
       </c>
       <c r="BK30" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL30" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BM30" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BN30" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BO30" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BP30" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="BQ30" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BR30" s="9" t="s">
         <v>133</v>
-      </c>
-      <c r="BQ30" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BR30" s="9" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:70">
@@ -9445,26 +9469,26 @@
         <v>418</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D31" s="12" t="str">
         <f t="shared" si="5"/>
         <v>418 玄泰T1</v>
       </c>
       <c r="E31" s="12" t="s">
+        <v>715</v>
+      </c>
+      <c r="F31" s="20" t="s">
         <v>716</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="G31" s="19">
+        <v>26.8</v>
+      </c>
+      <c r="H31" s="22" t="s">
         <v>717</v>
-      </c>
-      <c r="G31" s="19">
-        <v>27.3</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>718</v>
       </c>
       <c r="I31" s="22">
         <v>401</v>
@@ -9476,7 +9500,7 @@
         <v>21.25</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="R31" s="15">
         <v>34</v>
@@ -9488,7 +9512,7 @@
         <v>36</v>
       </c>
       <c r="Z31" s="9" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AA31" s="16">
         <v>160</v>
@@ -9497,52 +9521,52 @@
         <v>230</v>
       </c>
       <c r="AD31" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE31" s="9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AF31" s="10">
         <v>2026</v>
       </c>
       <c r="AG31" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="AH31" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI31" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="AH31" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI31" s="9" t="s">
+      <c r="AJ31" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK31" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL31" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="AM31" s="9" t="s">
         <v>723</v>
       </c>
-      <c r="AJ31" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK31" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL31" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="AM31" s="9" t="s">
+      <c r="AN31" s="9" t="s">
         <v>724</v>
       </c>
-      <c r="AN31" s="9" t="s">
+      <c r="AO31" s="9" t="s">
         <v>725</v>
       </c>
-      <c r="AO31" s="9" t="s">
+      <c r="AP31" s="9" t="s">
         <v>726</v>
       </c>
-      <c r="AP31" s="9" t="s">
+      <c r="AQ31" s="9" t="s">
+        <v>726</v>
+      </c>
+      <c r="AR31" s="9" t="s">
         <v>727</v>
       </c>
-      <c r="AQ31" s="9" t="s">
-        <v>727</v>
-      </c>
-      <c r="AR31" s="9" t="s">
+      <c r="AS31" s="9" t="s">
         <v>728</v>
-      </c>
-      <c r="AS31" s="9" t="s">
-        <v>729</v>
       </c>
       <c r="AU31" s="18">
         <v>0.33</v>
@@ -9551,7 +9575,7 @@
         <v>0.33</v>
       </c>
       <c r="AW31" s="9" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AX31" s="9">
         <v>264</v>
@@ -9566,43 +9590,43 @@
         <v>0.59189999999999998</v>
       </c>
       <c r="BB31" s="9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="BC31" s="9">
         <v>25</v>
       </c>
       <c r="BD31" s="9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="BE31" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="BF31" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BG31" s="19">
         <v>1</v>
       </c>
       <c r="BH31" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BI31" s="9" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="BJ31" s="19">
         <v>1848.19</v>
       </c>
       <c r="BK31" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="BL31" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BO31" s="9" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="BR31" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:70" ht="32">
@@ -9610,26 +9634,26 @@
         <v>314</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D32" s="12" t="str">
         <f t="shared" si="5"/>
         <v>314 大亮 泊</v>
       </c>
       <c r="E32" s="12" t="s">
+        <v>735</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>736</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>737</v>
       </c>
       <c r="G32" s="14">
         <v>33.700000000000003</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I32" s="13">
         <v>610</v>
@@ -9637,7 +9661,7 @@
       <c r="J32" s="14"/>
       <c r="K32" s="14"/>
       <c r="Q32" s="9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="R32" s="15">
         <v>38</v>
@@ -9654,7 +9678,7 @@
         <v>39</v>
       </c>
       <c r="Z32" s="9" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AA32" s="16">
         <v>185</v>
@@ -9666,49 +9690,49 @@
         <v>0.8</v>
       </c>
       <c r="AD32" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AE32" s="9" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AF32" s="10">
         <v>2026</v>
       </c>
       <c r="AG32" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="AH32" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AI32" s="27" t="s">
         <v>742</v>
       </c>
-      <c r="AH32" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI32" s="27" t="s">
+      <c r="AJ32" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK32" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AL32" s="9" t="s">
+        <v>623</v>
+      </c>
+      <c r="AM32" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="AN32" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="AJ32" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="AK32" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="AL32" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="AM32" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="AN32" s="9" t="s">
-        <v>744</v>
-      </c>
       <c r="AP32" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="AQ32" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="AR32" s="9" t="s">
         <v>628</v>
       </c>
-      <c r="AQ32" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="AR32" s="9" t="s">
-        <v>629</v>
-      </c>
       <c r="AS32" s="9" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AU32" s="18">
         <v>0.33900000000000002</v>
@@ -9717,7 +9741,7 @@
         <v>0.33900000000000002</v>
       </c>
       <c r="AW32" s="27" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AX32" s="9">
         <v>568</v>
@@ -9732,40 +9756,40 @@
         <v>0.63100000000000001</v>
       </c>
       <c r="BB32" s="9" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="BC32" s="9">
         <v>29</v>
       </c>
       <c r="BD32" s="18" t="s">
+        <v>746</v>
+      </c>
+      <c r="BE32" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="BF32" s="11" t="s">
         <v>747</v>
-      </c>
-      <c r="BE32" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="BF32" s="11" t="s">
-        <v>748</v>
       </c>
       <c r="BG32" s="19">
         <v>0.56000000000000005</v>
       </c>
       <c r="BH32" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BI32" s="9" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="BJ32" s="9">
         <v>2214</v>
       </c>
       <c r="BK32" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="BL32" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="BR32" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
